--- a/linearmodels/next_steps_data.xlsx
+++ b/linearmodels/next_steps_data.xlsx
@@ -5,12 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="sdrp_birds" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="sex_estimation" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="parasitoid" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="engagement" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="crmasses" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Bill Kristan</author>
   </authors>
@@ -38,27 +40,6 @@
           <t xml:space="preserve">Maximum length</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>17</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
@@ -71,27 +52,6 @@
           <t xml:space="preserve">Head diameter</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>17</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
@@ -104,34 +64,13 @@
           <t xml:space="preserve">Epicondylar breadth</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>17</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>BK</author>
   </authors>
@@ -143,32 +82,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Parent host species</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>1</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>69</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
@@ -177,32 +94,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Parent wing length</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>4</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
@@ -211,32 +106,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Parent thorax length</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>5</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="F1" authorId="0">
       <text>
@@ -245,32 +118,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Parent thorax depth</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>6</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="G1" authorId="0">
       <text>
@@ -279,32 +130,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Parent abdomen length</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>7</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="H1" authorId="0">
       <text>
@@ -313,32 +142,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Parent head depth</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>78</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="I1" authorId="0">
       <text>
@@ -347,32 +154,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Parent head length</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>-19</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="J1" authorId="0">
       <text>
@@ -381,32 +166,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Offspring host species</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>11</xdr:col>
-                <xdr:colOff>69</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="M1" authorId="0">
       <text>
@@ -415,32 +178,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Offspring wing length</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>13</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>15</xdr:col>
-                <xdr:colOff>18</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="N1" authorId="0">
       <text>
@@ -449,32 +190,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Offspring thorax length</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>14</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>16</xdr:col>
-                <xdr:colOff>18</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="O1" authorId="0">
       <text>
@@ -483,32 +202,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Offspring thorax depth</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>15</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>17</xdr:col>
-                <xdr:colOff>18</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="P1" authorId="0">
       <text>
@@ -517,32 +214,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Offspring abdomen length</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>16</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>18</xdr:col>
-                <xdr:colOff>18</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="Q1" authorId="0">
       <text>
@@ -551,32 +226,10 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Offspring head depth</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>17</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>18</xdr:col>
-                <xdr:colOff>75</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
     <comment ref="R1" authorId="0">
       <text>
@@ -585,39 +238,17 @@
             <sz val="10"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Offspring head length</t>
         </r>
       </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>18</xdr:col>
-                <xdr:colOff>23</xdr:colOff>
-                <xdr:row>0</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>19</xdr:col>
-                <xdr:colOff>47</xdr:colOff>
-                <xdr:row>3</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="268">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -1371,6 +1002,57 @@
   <si>
     <t xml:space="preserve">1_C7_into_Hc_4_G2_B_1Db2</t>
   </si>
+  <si>
+    <t xml:space="preserve">Likert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disagree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strongly disagree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strongly agree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Near campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moderately far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Really far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parasite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatment</t>
+  </si>
 </sst>
 </file>
 
@@ -1384,6 +1066,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1405,12 +1088,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -1510,39 +1193,43 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1570,6 +1257,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1578,12 +1269,12 @@
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Pivot Table Corner" xfId="20"/>
-    <cellStyle name="Pivot Table Value" xfId="21"/>
+    <cellStyle name="Pivot Table Category" xfId="20"/>
+    <cellStyle name="Pivot Table Corner" xfId="21"/>
     <cellStyle name="Pivot Table Field" xfId="22"/>
-    <cellStyle name="Pivot Table Category" xfId="23"/>
+    <cellStyle name="Pivot Table Result" xfId="23"/>
     <cellStyle name="Pivot Table Title" xfId="24"/>
-    <cellStyle name="Pivot Table Result" xfId="25"/>
+    <cellStyle name="Pivot Table Value" xfId="25"/>
   </cellStyles>
 </styleSheet>
 </file>
@@ -1596,37 +1287,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -35072,1447 +34763,1447 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>343</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>49.86</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>61</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>326</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>38.89</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>311</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>40.7</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>310</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>42.89</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>341</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>297</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>38.56</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>287</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>42.1</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>348</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>42.18</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>343</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>51.49</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>308</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>50.38</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="1" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>296</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>35.47</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>329</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>44.81</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>316</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>45.77</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>341</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>48.49</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>61</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>317</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <v>47.81</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>304</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>39.32</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>364</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <v>56.61</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="1" t="n">
         <v>307</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="1" t="n">
         <v>41.05</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="1" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>350</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="1" t="n">
         <v>50.32</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="1" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="1" t="n">
         <v>337</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="1" t="n">
         <v>48.26</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="1" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="1" t="n">
         <v>315</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="D22" s="1" t="n">
         <v>43.23</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="1" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="1" t="n">
         <v>328</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="1" t="n">
         <v>40.47</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="1" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="1" t="n">
         <v>317</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24" s="1" t="n">
         <v>45.93</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="1" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="1" t="n">
         <v>337</v>
       </c>
-      <c r="D25" s="0" t="n">
+      <c r="D25" s="1" t="n">
         <v>50.83</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="1" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="1" t="n">
         <v>317</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26" s="1" t="n">
         <v>42.99</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="1" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="1" t="n">
         <v>334</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="1" t="n">
         <v>47.87</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="1" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="1" t="n">
         <v>338</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28" s="1" t="n">
         <v>42.15</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="1" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="1" t="n">
         <v>370</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="1" t="n">
         <v>53.45</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="1" t="n">
         <v>283</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D30" s="1" t="n">
         <v>38.63</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="1" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="1" t="n">
         <v>346</v>
       </c>
-      <c r="D31" s="0" t="n">
+      <c r="D31" s="1" t="n">
         <v>49.31</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="1" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="1" t="n">
         <v>282</v>
       </c>
-      <c r="D32" s="0" t="n">
+      <c r="D32" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="1" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="1" t="n">
         <v>377</v>
       </c>
-      <c r="D33" s="0" t="n">
+      <c r="D33" s="1" t="n">
         <v>55.19</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="1" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="1" t="n">
         <v>331</v>
       </c>
-      <c r="D34" s="0" t="n">
+      <c r="D34" s="1" t="n">
         <v>48.74</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="1" t="n">
         <v>290</v>
       </c>
-      <c r="D35" s="0" t="n">
+      <c r="D35" s="1" t="n">
         <v>41.15</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="1" t="n">
         <v>291</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36" s="1" t="n">
         <v>41.07</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="1" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="1" t="n">
         <v>305</v>
       </c>
-      <c r="D37" s="0" t="n">
+      <c r="D37" s="1" t="n">
         <v>42.92</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="1" t="n">
         <v>327</v>
       </c>
-      <c r="D38" s="0" t="n">
+      <c r="D38" s="1" t="n">
         <v>42.07</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="1" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="1" t="n">
         <v>336</v>
       </c>
-      <c r="D39" s="0" t="n">
+      <c r="D39" s="1" t="n">
         <v>47.97</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="1" t="n">
         <v>293</v>
       </c>
-      <c r="D40" s="0" t="n">
+      <c r="D40" s="1" t="n">
         <v>43.25</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="1" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41" s="1" t="n">
         <v>319</v>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D41" s="1" t="n">
         <v>51.04</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C42" s="0" t="n">
+      <c r="C42" s="1" t="n">
         <v>319</v>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42" s="1" t="n">
         <v>51.95</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="1" t="n">
         <v>66</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C43" s="0" t="n">
+      <c r="C43" s="1" t="n">
         <v>313</v>
       </c>
-      <c r="D43" s="0" t="n">
+      <c r="D43" s="1" t="n">
         <v>42.44</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="1" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="1" t="n">
         <v>338</v>
       </c>
-      <c r="D44" s="0" t="n">
+      <c r="D44" s="1" t="n">
         <v>42.63</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="1" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="0" t="n">
+      <c r="C45" s="1" t="n">
         <v>293</v>
       </c>
-      <c r="D45" s="0" t="n">
+      <c r="D45" s="1" t="n">
         <v>40.81</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="1" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="0" t="n">
+      <c r="C46" s="1" t="n">
         <v>315</v>
       </c>
-      <c r="D46" s="0" t="n">
+      <c r="D46" s="1" t="n">
         <v>43.44</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46" s="1" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C47" s="0" t="n">
+      <c r="C47" s="1" t="n">
         <v>324</v>
       </c>
-      <c r="D47" s="0" t="n">
+      <c r="D47" s="1" t="n">
         <v>41.91</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="1" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="D48" s="0" t="n">
+      <c r="D48" s="1" t="n">
         <v>46.19</v>
       </c>
-      <c r="E48" s="0" t="n">
+      <c r="E48" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="0" t="n">
+      <c r="C49" s="1" t="n">
         <v>316</v>
       </c>
-      <c r="D49" s="0" t="n">
+      <c r="D49" s="1" t="n">
         <v>40.6</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49" s="1" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="1" t="n">
         <v>331</v>
       </c>
-      <c r="D50" s="0" t="n">
+      <c r="D50" s="1" t="n">
         <v>47.9</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50" s="1" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="1" t="n">
         <v>339</v>
       </c>
-      <c r="D51" s="0" t="n">
+      <c r="D51" s="1" t="n">
         <v>42.17</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="1" t="n">
         <v>383</v>
       </c>
-      <c r="D52" s="0" t="n">
+      <c r="D52" s="1" t="n">
         <v>51.57</v>
       </c>
-      <c r="E52" s="0" t="n">
+      <c r="E52" s="1" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="D53" s="0" t="n">
+      <c r="D53" s="1" t="n">
         <v>41.25</v>
       </c>
-      <c r="E53" s="0" t="n">
+      <c r="E53" s="1" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="0" t="n">
+      <c r="C54" s="1" t="n">
         <v>331</v>
       </c>
-      <c r="D54" s="0" t="n">
+      <c r="D54" s="1" t="n">
         <v>42.24</v>
       </c>
-      <c r="E54" s="0" t="n">
+      <c r="E54" s="1" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C55" s="0" t="n">
+      <c r="C55" s="1" t="n">
         <v>374</v>
       </c>
-      <c r="D55" s="0" t="n">
+      <c r="D55" s="1" t="n">
         <v>49.68</v>
       </c>
-      <c r="E55" s="0" t="n">
+      <c r="E55" s="1" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56" s="1" t="n">
         <v>334</v>
       </c>
-      <c r="D56" s="0" t="n">
+      <c r="D56" s="1" t="n">
         <v>48.19</v>
       </c>
-      <c r="E56" s="0" t="n">
+      <c r="E56" s="1" t="n">
         <v>61</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="0" t="n">
+      <c r="C57" s="1" t="n">
         <v>343</v>
       </c>
-      <c r="D57" s="0" t="n">
+      <c r="D57" s="1" t="n">
         <v>51.56</v>
       </c>
-      <c r="E57" s="0" t="n">
+      <c r="E57" s="1" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C58" s="0" t="n">
+      <c r="C58" s="1" t="n">
         <v>322</v>
       </c>
-      <c r="D58" s="0" t="n">
+      <c r="D58" s="1" t="n">
         <v>43.94</v>
       </c>
-      <c r="E58" s="0" t="n">
+      <c r="E58" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C59" s="0" t="n">
+      <c r="C59" s="1" t="n">
         <v>340</v>
       </c>
-      <c r="D59" s="0" t="n">
+      <c r="D59" s="1" t="n">
         <v>48.78</v>
       </c>
-      <c r="E59" s="0" t="n">
+      <c r="E59" s="1" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C60" s="0" t="n">
+      <c r="C60" s="1" t="n">
         <v>311</v>
       </c>
-      <c r="D60" s="0" t="n">
+      <c r="D60" s="1" t="n">
         <v>40.94</v>
       </c>
-      <c r="E60" s="0" t="n">
+      <c r="E60" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C61" s="0" t="n">
+      <c r="C61" s="1" t="n">
         <v>289</v>
       </c>
-      <c r="D61" s="0" t="n">
+      <c r="D61" s="1" t="n">
         <v>38.22</v>
       </c>
-      <c r="E61" s="0" t="n">
+      <c r="E61" s="1" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C62" s="0" t="n">
+      <c r="C62" s="1" t="n">
         <v>353</v>
       </c>
-      <c r="D62" s="0" t="n">
+      <c r="D62" s="1" t="n">
         <v>49.53</v>
       </c>
-      <c r="E62" s="0" t="n">
+      <c r="E62" s="1" t="n">
         <v>68</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C63" s="0" t="n">
+      <c r="C63" s="1" t="n">
         <v>341</v>
       </c>
-      <c r="D63" s="0" t="n">
+      <c r="D63" s="1" t="n">
         <v>47.34</v>
       </c>
-      <c r="E63" s="0" t="n">
+      <c r="E63" s="1" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C64" s="0" t="n">
+      <c r="C64" s="1" t="n">
         <v>350</v>
       </c>
-      <c r="D64" s="0" t="n">
+      <c r="D64" s="1" t="n">
         <v>48.15</v>
       </c>
-      <c r="E64" s="0" t="n">
+      <c r="E64" s="1" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C65" s="0" t="n">
+      <c r="C65" s="1" t="n">
         <v>342</v>
       </c>
-      <c r="D65" s="0" t="n">
+      <c r="D65" s="1" t="n">
         <v>47.22</v>
       </c>
-      <c r="E65" s="0" t="n">
+      <c r="E65" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C66" s="0" t="n">
+      <c r="C66" s="1" t="n">
         <v>322</v>
       </c>
-      <c r="D66" s="0" t="n">
+      <c r="D66" s="1" t="n">
         <v>46.46</v>
       </c>
-      <c r="E66" s="0" t="n">
+      <c r="E66" s="1" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C67" s="0" t="n">
+      <c r="C67" s="1" t="n">
         <v>322</v>
       </c>
-      <c r="D67" s="0" t="n">
+      <c r="D67" s="1" t="n">
         <v>51.35</v>
       </c>
-      <c r="E67" s="0" t="n">
+      <c r="E67" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C68" s="0" t="n">
+      <c r="C68" s="1" t="n">
         <v>311</v>
       </c>
-      <c r="D68" s="0" t="n">
+      <c r="D68" s="1" t="n">
         <v>41.01</v>
       </c>
-      <c r="E68" s="0" t="n">
+      <c r="E68" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C69" s="0" t="n">
+      <c r="C69" s="1" t="n">
         <v>371</v>
       </c>
-      <c r="D69" s="0" t="n">
+      <c r="D69" s="1" t="n">
         <v>50.24</v>
       </c>
-      <c r="E69" s="0" t="n">
+      <c r="E69" s="1" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C70" s="0" t="n">
+      <c r="C70" s="1" t="n">
         <v>319</v>
       </c>
-      <c r="D70" s="0" t="n">
+      <c r="D70" s="1" t="n">
         <v>44.38</v>
       </c>
-      <c r="E70" s="0" t="n">
+      <c r="E70" s="1" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C71" s="0" t="n">
+      <c r="C71" s="1" t="n">
         <v>306</v>
       </c>
-      <c r="D71" s="0" t="n">
+      <c r="D71" s="1" t="n">
         <v>39.09</v>
       </c>
-      <c r="E71" s="0" t="n">
+      <c r="E71" s="1" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C72" s="0" t="n">
+      <c r="C72" s="1" t="n">
         <v>342</v>
       </c>
-      <c r="D72" s="0" t="n">
+      <c r="D72" s="1" t="n">
         <v>49.83</v>
       </c>
-      <c r="E72" s="0" t="n">
+      <c r="E72" s="1" t="n">
         <v>63</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C73" s="0" t="n">
+      <c r="C73" s="1" t="n">
         <v>286</v>
       </c>
-      <c r="D73" s="0" t="n">
+      <c r="D73" s="1" t="n">
         <v>41.23</v>
       </c>
-      <c r="E73" s="0" t="n">
+      <c r="E73" s="1" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C74" s="0" t="n">
+      <c r="C74" s="1" t="n">
         <v>312</v>
       </c>
-      <c r="D74" s="0" t="n">
+      <c r="D74" s="1" t="n">
         <v>42.17</v>
       </c>
-      <c r="E74" s="0" t="n">
+      <c r="E74" s="1" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C75" s="0" t="n">
+      <c r="C75" s="1" t="n">
         <v>314</v>
       </c>
-      <c r="D75" s="0" t="n">
+      <c r="D75" s="1" t="n">
         <v>45.65</v>
       </c>
-      <c r="E75" s="0" t="n">
+      <c r="E75" s="1" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C76" s="0" t="n">
+      <c r="C76" s="1" t="n">
         <v>293</v>
       </c>
-      <c r="D76" s="0" t="n">
+      <c r="D76" s="1" t="n">
         <v>41.48</v>
       </c>
-      <c r="E76" s="0" t="n">
+      <c r="E76" s="1" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C77" s="0" t="n">
+      <c r="C77" s="1" t="n">
         <v>374</v>
       </c>
-      <c r="D77" s="0" t="n">
+      <c r="D77" s="1" t="n">
         <v>39.9</v>
       </c>
-      <c r="E77" s="0" t="n">
+      <c r="E77" s="1" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C78" s="0" t="n">
+      <c r="C78" s="1" t="n">
         <v>318</v>
       </c>
-      <c r="D78" s="0" t="n">
+      <c r="D78" s="1" t="n">
         <v>42.32</v>
       </c>
-      <c r="E78" s="0" t="n">
+      <c r="E78" s="1" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C79" s="0" t="n">
+      <c r="C79" s="1" t="n">
         <v>294</v>
       </c>
-      <c r="D79" s="0" t="n">
+      <c r="D79" s="1" t="n">
         <v>40.86</v>
       </c>
-      <c r="E79" s="0" t="n">
+      <c r="E79" s="1" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C80" s="0" t="n">
+      <c r="C80" s="1" t="n">
         <v>322</v>
       </c>
-      <c r="D80" s="0" t="n">
+      <c r="D80" s="1" t="n">
         <v>48.61</v>
       </c>
-      <c r="E80" s="0" t="n">
+      <c r="E80" s="1" t="n">
         <v>59</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C81" s="0" t="n">
+      <c r="C81" s="1" t="n">
         <v>298</v>
       </c>
-      <c r="D81" s="0" t="n">
+      <c r="D81" s="1" t="n">
         <v>41.02</v>
       </c>
-      <c r="E81" s="0" t="n">
+      <c r="E81" s="1" t="n">
         <v>57</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C82" s="0" t="n">
+      <c r="C82" s="1" t="n">
         <v>302</v>
       </c>
-      <c r="D82" s="0" t="n">
+      <c r="D82" s="1" t="n">
         <v>41.83</v>
       </c>
-      <c r="E82" s="0" t="n">
+      <c r="E82" s="1" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C83" s="0" t="n">
+      <c r="C83" s="1" t="n">
         <v>333</v>
       </c>
-      <c r="D83" s="0" t="n">
+      <c r="D83" s="1" t="n">
         <v>51.8</v>
       </c>
-      <c r="E83" s="0" t="n">
+      <c r="E83" s="1" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C84" s="0" t="n">
+      <c r="C84" s="1" t="n">
         <v>304</v>
       </c>
-      <c r="D84" s="0" t="n">
+      <c r="D84" s="1" t="n">
         <v>41.29</v>
       </c>
-      <c r="E84" s="0" t="n">
+      <c r="E84" s="1" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C85" s="0" t="n">
+      <c r="C85" s="1" t="n">
         <v>291</v>
       </c>
-      <c r="D85" s="0" t="n">
+      <c r="D85" s="1" t="n">
         <v>38.53</v>
       </c>
-      <c r="E85" s="0" t="n">
+      <c r="E85" s="1" t="n">
         <v>53</v>
       </c>
     </row>
@@ -36536,2309 +36227,2309 @@
   <dimension ref="A1:R41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="20.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="33.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="2" width="7.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="20.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="8.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="36.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="13" style="2" width="7.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="1" width="7.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="8.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="36.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="13" style="1" width="7.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="3" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="7" t="n">
         <v>2.8716</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="7" t="n">
         <v>1.1718</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="7" t="n">
         <v>0.838</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="7" t="n">
         <v>1.9033</v>
       </c>
-      <c r="H2" s="8" t="n">
+      <c r="H2" s="7" t="n">
         <v>0.4696</v>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="I2" s="7" t="n">
         <v>0.7224</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="M2" s="8" t="n">
+      <c r="M2" s="7" t="n">
         <v>3.1892</v>
       </c>
-      <c r="N2" s="8" t="n">
+      <c r="N2" s="7" t="n">
         <v>1.6558</v>
       </c>
-      <c r="O2" s="8" t="n">
+      <c r="O2" s="7" t="n">
         <v>1.2358</v>
       </c>
-      <c r="P2" s="8" t="n">
+      <c r="P2" s="7" t="n">
         <v>2.5087</v>
       </c>
-      <c r="Q2" s="8" t="n">
+      <c r="Q2" s="7" t="n">
         <v>0.7561</v>
       </c>
-      <c r="R2" s="8" t="n">
+      <c r="R2" s="7" t="n">
         <v>1.0449</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="7" t="n">
         <v>3.1977</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="7" t="n">
         <v>1.467</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="7" t="n">
         <v>0.9121</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="7" t="n">
         <v>2.0315</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="7" t="n">
         <v>0.5982</v>
       </c>
-      <c r="I3" s="8" t="n">
+      <c r="I3" s="7" t="n">
         <v>0.8574</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="7" t="n">
         <v>2.9078</v>
       </c>
-      <c r="N3" s="8" t="n">
+      <c r="N3" s="7" t="n">
         <v>1.2282</v>
       </c>
-      <c r="O3" s="8" t="n">
+      <c r="O3" s="7" t="n">
         <v>0.8033</v>
       </c>
-      <c r="P3" s="8" t="n">
+      <c r="P3" s="7" t="n">
         <v>1.9146</v>
       </c>
-      <c r="Q3" s="8" t="n">
+      <c r="Q3" s="7" t="n">
         <v>0.4885</v>
       </c>
-      <c r="R3" s="8" t="n">
+      <c r="R3" s="7" t="n">
         <v>0.7563</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="7" t="n">
         <v>2.932</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="7" t="n">
         <v>1.816</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="7" t="n">
         <v>1.0538</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="7" t="n">
         <v>2.5526</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="7" t="n">
         <v>0.5573</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="7" t="n">
         <v>0.9272</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="7" t="n">
         <v>2.875</v>
       </c>
-      <c r="N4" s="8" t="n">
+      <c r="N4" s="7" t="n">
         <v>1.3972</v>
       </c>
-      <c r="O4" s="8" t="n">
+      <c r="O4" s="7" t="n">
         <v>0.8829</v>
       </c>
-      <c r="P4" s="8" t="n">
+      <c r="P4" s="7" t="n">
         <v>2.5017</v>
       </c>
-      <c r="Q4" s="8" t="n">
+      <c r="Q4" s="7" t="n">
         <v>0.4809</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="7" t="n">
         <v>0.8526</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="7" t="n">
         <v>2.0785</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="7" t="n">
         <v>1.316</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="7" t="n">
         <v>0.8622</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="7" t="n">
         <v>2.259</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="7" t="n">
         <v>0.5524</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="7" t="n">
         <v>0.7949</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="7" t="n">
         <v>3.7744</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="7" t="n">
         <v>1.5158</v>
       </c>
-      <c r="O5" s="8" t="n">
+      <c r="O5" s="7" t="n">
         <v>0.9572</v>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="P5" s="7" t="n">
         <v>2.5386</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="7" t="n">
         <v>0.5404</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="7" t="n">
         <v>0.8327</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="7" t="n">
         <v>3.5233</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="7" t="n">
         <v>1.4953</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="7" t="n">
         <v>1.0745</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="7" t="n">
         <v>2.2396</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="7" t="n">
         <v>0.6081</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="7" t="n">
         <v>0.8687</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="7" t="n">
         <v>2.8214</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="7" t="n">
         <v>1.2627</v>
       </c>
-      <c r="O6" s="8" t="n">
+      <c r="O6" s="7" t="n">
         <v>0.8533</v>
       </c>
-      <c r="P6" s="8" t="n">
+      <c r="P6" s="7" t="n">
         <v>1.7828</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="7" t="n">
         <v>0.5219</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="7" t="n">
         <v>0.7278</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="7" t="n">
         <v>2.264</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="7" t="n">
         <v>1.2997</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="7" t="n">
         <v>0.7553</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="7" t="n">
         <v>1.9111</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="7" t="n">
         <v>0.4515</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="7" t="n">
         <v>0.6962</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="7" t="n">
         <v>3.2245</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="7" t="n">
         <v>1.441</v>
       </c>
-      <c r="O7" s="8" t="n">
+      <c r="O7" s="7" t="n">
         <v>0.9267</v>
       </c>
-      <c r="P7" s="8" t="n">
+      <c r="P7" s="7" t="n">
         <v>2.4216</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="7" t="n">
         <v>0.5195</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="7" t="n">
         <v>0.8149</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>2.264</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>1.2997</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="7" t="n">
         <v>0.7553</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
         <v>1.9111</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="7" t="n">
         <v>0.4515</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="7" t="n">
         <v>0.6962</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="7" t="n">
         <v>2.6647</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="7" t="n">
         <v>1.2905</v>
       </c>
-      <c r="O8" s="8" t="n">
+      <c r="O8" s="7" t="n">
         <v>0.8423</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="P8" s="7" t="n">
         <v>2.1447</v>
       </c>
-      <c r="Q8" s="8" t="n">
+      <c r="Q8" s="7" t="n">
         <v>0.5341</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="7" t="n">
         <v>0.7365</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="7" t="n">
         <v>3.1558</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="7" t="n">
         <v>1.595</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="7" t="n">
         <v>1.1298</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="G9" s="7" t="n">
         <v>2.3446</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="7" t="n">
         <v>0.613</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="7" t="n">
         <v>0.9286</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="7" t="n">
         <v>3.006</v>
       </c>
-      <c r="N9" s="8" t="n">
+      <c r="N9" s="7" t="n">
         <v>1.305</v>
       </c>
-      <c r="O9" s="8" t="n">
+      <c r="O9" s="7" t="n">
         <v>0.8668</v>
       </c>
-      <c r="P9" s="8" t="n">
+      <c r="P9" s="7" t="n">
         <v>2.0118</v>
       </c>
-      <c r="Q9" s="8" t="n">
+      <c r="Q9" s="7" t="n">
         <v>0.5738</v>
       </c>
-      <c r="R9" s="8" t="n">
+      <c r="R9" s="7" t="n">
         <v>0.8537</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="7" t="n">
         <v>3.1558</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="7" t="n">
         <v>1.595</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="7" t="n">
         <v>1.1298</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="7" t="n">
         <v>2.3446</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="7" t="n">
         <v>0.613</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I10" s="7" t="n">
         <v>0.9286</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="7" t="n">
         <v>3.3953</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="7" t="n">
         <v>1.4112</v>
       </c>
-      <c r="O10" s="8" t="n">
+      <c r="O10" s="7" t="n">
         <v>1.0163</v>
       </c>
-      <c r="P10" s="8" t="n">
+      <c r="P10" s="7" t="n">
         <v>1.8795</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="7" t="n">
         <v>0.7455</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="7" t="n">
         <v>0.9623</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="7" t="n">
         <v>2.264</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="7" t="n">
         <v>1.2997</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="7" t="n">
         <v>0.7553</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="7" t="n">
         <v>1.9111</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="7" t="n">
         <v>0.4515</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="7" t="n">
         <v>0.6962</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" s="7" t="n">
         <v>2.6647</v>
       </c>
-      <c r="N11" s="8" t="n">
+      <c r="N11" s="7" t="n">
         <v>1.2905</v>
       </c>
-      <c r="O11" s="8" t="n">
+      <c r="O11" s="7" t="n">
         <v>0.8423</v>
       </c>
-      <c r="P11" s="8" t="n">
+      <c r="P11" s="7" t="n">
         <v>2.1447</v>
       </c>
-      <c r="Q11" s="8" t="n">
+      <c r="Q11" s="7" t="n">
         <v>0.5341</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="7" t="n">
         <v>0.7365</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="7" t="n">
         <v>3.1558</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="7" t="n">
         <v>1.595</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="7" t="n">
         <v>1.1298</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="7" t="n">
         <v>2.3446</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="7" t="n">
         <v>0.613</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="I12" s="7" t="n">
         <v>0.9286</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="7" t="n">
         <v>3.006</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="7" t="n">
         <v>1.305</v>
       </c>
-      <c r="O12" s="8" t="n">
+      <c r="O12" s="7" t="n">
         <v>0.8668</v>
       </c>
-      <c r="P12" s="8" t="n">
+      <c r="P12" s="7" t="n">
         <v>2.0118</v>
       </c>
-      <c r="Q12" s="8" t="n">
+      <c r="Q12" s="7" t="n">
         <v>0.5738</v>
       </c>
-      <c r="R12" s="8" t="n">
+      <c r="R12" s="7" t="n">
         <v>0.8537</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="7" t="n">
         <v>3.1558</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="7" t="n">
         <v>1.595</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="7" t="n">
         <v>1.1298</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="7" t="n">
         <v>2.3446</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="7" t="n">
         <v>0.613</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="7" t="n">
         <v>0.9286</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="7" t="n">
         <v>3.3953</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="7" t="n">
         <v>1.4112</v>
       </c>
-      <c r="O13" s="8" t="n">
+      <c r="O13" s="7" t="n">
         <v>1.0163</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="P13" s="7" t="n">
         <v>1.8795</v>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="Q13" s="7" t="n">
         <v>0.7455</v>
       </c>
-      <c r="R13" s="8" t="n">
+      <c r="R13" s="7" t="n">
         <v>0.9623</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="7" t="n">
         <v>3.6232</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="7" t="n">
         <v>1.5946</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="7" t="n">
         <v>1.0584</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="7" t="n">
         <v>2.1651</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="7" t="n">
         <v>0.6704</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I14" s="7" t="n">
         <v>1.0121</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="7" t="n">
         <v>3.6176</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="7" t="n">
         <v>1.557</v>
       </c>
-      <c r="O14" s="8" t="n">
+      <c r="O14" s="7" t="n">
         <v>0.985</v>
       </c>
-      <c r="P14" s="8" t="n">
+      <c r="P14" s="7" t="n">
         <v>2.1746</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="7" t="n">
         <v>0.6062</v>
       </c>
-      <c r="R14" s="8" t="n">
+      <c r="R14" s="7" t="n">
         <v>0.9236</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="7" t="n">
         <v>2.4653</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="7" t="n">
         <v>1.091</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="7" t="n">
         <v>0.7012</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="7" t="n">
         <v>1.633</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="7" t="n">
         <v>0.4758</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="7" t="n">
         <v>0.6512</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="7" t="n">
         <v>2.6018</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="N15" s="7" t="n">
         <v>1.4118</v>
       </c>
-      <c r="O15" s="8" t="n">
+      <c r="O15" s="7" t="n">
         <v>0.9388</v>
       </c>
-      <c r="P15" s="8" t="n">
+      <c r="P15" s="7" t="n">
         <v>1.7673</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="7" t="n">
         <v>0.5478</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="R15" s="7" t="n">
         <v>0.7955</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="7" t="n">
         <v>2.4653</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="7" t="n">
         <v>1.091</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="7" t="n">
         <v>0.7012</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="7" t="n">
         <v>1.633</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="H16" s="7" t="n">
         <v>0.4758</v>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="I16" s="7" t="n">
         <v>0.6512</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="L16" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="7" t="n">
         <v>2.612</v>
       </c>
-      <c r="N16" s="8" t="n">
+      <c r="N16" s="7" t="n">
         <v>1.432</v>
       </c>
-      <c r="O16" s="8" t="n">
+      <c r="O16" s="7" t="n">
         <v>0.965</v>
       </c>
-      <c r="P16" s="8" t="n">
+      <c r="P16" s="7" t="n">
         <v>2.577</v>
       </c>
-      <c r="Q16" s="8" t="n">
+      <c r="Q16" s="7" t="n">
         <v>0.577</v>
       </c>
-      <c r="R16" s="8" t="n">
+      <c r="R16" s="7" t="n">
         <v>0.983</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="7" t="n">
         <v>2.4653</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="7" t="n">
         <v>1.091</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="7" t="n">
         <v>0.7012</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="7" t="n">
         <v>1.633</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="7" t="n">
         <v>0.4758</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="7" t="n">
         <v>0.6512</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="7" t="n">
         <v>2.9493</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="7" t="n">
         <v>1.3057</v>
       </c>
-      <c r="O17" s="8" t="n">
+      <c r="O17" s="7" t="n">
         <v>0.7483</v>
       </c>
-      <c r="P17" s="8" t="n">
+      <c r="P17" s="7" t="n">
         <v>1.731</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="7" t="n">
         <v>0.5227</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="7" t="n">
         <v>0.744</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="7" t="n">
         <v>2.6146</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="7" t="n">
         <v>1.2315</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="7" t="n">
         <v>0.8891</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="7" t="n">
         <v>1.5082</v>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H18" s="7" t="n">
         <v>0.562</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="7" t="n">
         <v>0.7938</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="M18" s="8" t="n">
+      <c r="M18" s="7" t="n">
         <v>2.731</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="N18" s="7" t="n">
         <v>1.2463</v>
       </c>
-      <c r="O18" s="8" t="n">
+      <c r="O18" s="7" t="n">
         <v>0.795</v>
       </c>
-      <c r="P18" s="8" t="n">
+      <c r="P18" s="7" t="n">
         <v>1.5483</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="Q18" s="7" t="n">
         <v>0.4927</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="7" t="n">
         <v>0.781</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="7" t="n">
         <v>2.4498</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="7" t="n">
         <v>1.3392</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="F19" s="7" t="n">
         <v>0.679</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G19" s="7" t="n">
         <v>1.459</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="7" t="n">
         <v>0.4752</v>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="7" t="n">
         <v>0.6936</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="L19" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="7" t="n">
         <v>2.197</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="7" t="n">
         <v>1.1258</v>
       </c>
-      <c r="O19" s="8" t="n">
+      <c r="O19" s="7" t="n">
         <v>0.7641</v>
       </c>
-      <c r="P19" s="8" t="n">
+      <c r="P19" s="7" t="n">
         <v>1.5856</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="7" t="n">
         <v>0.4705</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="7" t="n">
         <v>0.7329</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="7" t="n">
         <v>2.4498</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="7" t="n">
         <v>1.3392</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="7" t="n">
         <v>0.679</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="7" t="n">
         <v>1.459</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="7" t="n">
         <v>0.4752</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="7" t="n">
         <v>0.6936</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="7" t="n">
         <v>2.9829</v>
       </c>
-      <c r="N20" s="8" t="n">
+      <c r="N20" s="7" t="n">
         <v>1.3883</v>
       </c>
-      <c r="O20" s="8" t="n">
+      <c r="O20" s="7" t="n">
         <v>0.8669</v>
       </c>
-      <c r="P20" s="8" t="n">
+      <c r="P20" s="7" t="n">
         <v>1.9023</v>
       </c>
-      <c r="Q20" s="8" t="n">
+      <c r="Q20" s="7" t="n">
         <v>0.5163</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="R20" s="7" t="n">
         <v>0.7712</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="7" t="n">
         <v>2.4498</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="7" t="n">
         <v>1.3392</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="7" t="n">
         <v>0.679</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="7" t="n">
         <v>1.459</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="7" t="n">
         <v>0.4752</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="7" t="n">
         <v>0.6936</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="7" t="n">
         <v>3.015</v>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="N21" s="7" t="n">
         <v>1.3007</v>
       </c>
-      <c r="O21" s="8" t="n">
+      <c r="O21" s="7" t="n">
         <v>0.9085</v>
       </c>
-      <c r="P21" s="8" t="n">
+      <c r="P21" s="7" t="n">
         <v>1.9364</v>
       </c>
-      <c r="Q21" s="8" t="n">
+      <c r="Q21" s="7" t="n">
         <v>0.504</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="R21" s="7" t="n">
         <v>0.7965</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="7" t="n">
         <v>3.1892</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="7" t="n">
         <v>1.6558</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="7" t="n">
         <v>1.2358</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="7" t="n">
         <v>2.5087</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="7" t="n">
         <v>0.7561</v>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I22" s="7" t="n">
         <v>1.0449</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="L22" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="7" t="n">
         <v>3.6682</v>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="N22" s="7" t="n">
         <v>1.4984</v>
       </c>
-      <c r="O22" s="8" t="n">
+      <c r="O22" s="7" t="n">
         <v>0.9682</v>
       </c>
-      <c r="P22" s="8" t="n">
+      <c r="P22" s="7" t="n">
         <v>2.1977</v>
       </c>
-      <c r="Q22" s="8" t="n">
+      <c r="Q22" s="7" t="n">
         <v>0.5235</v>
       </c>
-      <c r="R22" s="8" t="n">
+      <c r="R22" s="7" t="n">
         <v>0.8107</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D23" s="7" t="n">
         <v>2.875</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="7" t="n">
         <v>1.3972</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="7" t="n">
         <v>0.8829</v>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G23" s="7" t="n">
         <v>2.5017</v>
       </c>
-      <c r="H23" s="8" t="n">
+      <c r="H23" s="7" t="n">
         <v>0.4809</v>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" s="7" t="n">
         <v>0.8526</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="K23" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="M23" s="7" t="n">
         <v>2.295</v>
       </c>
-      <c r="N23" s="8" t="n">
+      <c r="N23" s="7" t="n">
         <v>1.4486</v>
       </c>
-      <c r="O23" s="8" t="n">
+      <c r="O23" s="7" t="n">
         <v>1.0382</v>
       </c>
-      <c r="P23" s="8" t="n">
+      <c r="P23" s="7" t="n">
         <v>2.349</v>
       </c>
-      <c r="Q23" s="8" t="n">
+      <c r="Q23" s="7" t="n">
         <v>0.5444</v>
       </c>
-      <c r="R23" s="8" t="n">
+      <c r="R23" s="7" t="n">
         <v>0.8466</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="7" t="n">
         <v>3.6828</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="7" t="n">
         <v>1.4242</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="7" t="n">
         <v>1.0185</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G24" s="7" t="n">
         <v>2.3916</v>
       </c>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="7" t="n">
         <v>0.5844</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I24" s="7" t="n">
         <v>0.8354</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="L24" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="7" t="n">
         <v>2.608</v>
       </c>
-      <c r="N24" s="8" t="n">
+      <c r="N24" s="7" t="n">
         <v>1.4388</v>
       </c>
-      <c r="O24" s="8" t="n">
+      <c r="O24" s="7" t="n">
         <v>1.017</v>
       </c>
-      <c r="P24" s="8" t="n">
+      <c r="P24" s="7" t="n">
         <v>2.3581</v>
       </c>
-      <c r="Q24" s="8" t="n">
+      <c r="Q24" s="7" t="n">
         <v>0.5238</v>
       </c>
-      <c r="R24" s="8" t="n">
+      <c r="R24" s="7" t="n">
         <v>0.8115</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="7" t="n">
         <v>3.2245</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="7" t="n">
         <v>1.441</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="7" t="n">
         <v>0.9267</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G25" s="7" t="n">
         <v>2.4216</v>
       </c>
-      <c r="H25" s="8" t="n">
+      <c r="H25" s="7" t="n">
         <v>0.5195</v>
       </c>
-      <c r="I25" s="8" t="n">
+      <c r="I25" s="7" t="n">
         <v>0.8149</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="L25" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="7" t="n">
         <v>3.474</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="N25" s="7" t="n">
         <v>1.568</v>
       </c>
-      <c r="O25" s="8" t="n">
+      <c r="O25" s="7" t="n">
         <v>1.0147</v>
       </c>
-      <c r="P25" s="8" t="n">
+      <c r="P25" s="7" t="n">
         <v>2.3944</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="Q25" s="7" t="n">
         <v>0.5888</v>
       </c>
-      <c r="R25" s="8" t="n">
+      <c r="R25" s="7" t="n">
         <v>0.8627</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="D26" s="8" t="n">
+      <c r="D26" s="7" t="n">
         <v>3.474</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="7" t="n">
         <v>1.568</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="7" t="n">
         <v>1.0147</v>
       </c>
-      <c r="G26" s="8" t="n">
+      <c r="G26" s="7" t="n">
         <v>2.3944</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="7" t="n">
         <v>0.5888</v>
       </c>
-      <c r="I26" s="8" t="n">
+      <c r="I26" s="7" t="n">
         <v>0.8627</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="L26" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="7" t="n">
         <v>3.1558</v>
       </c>
-      <c r="N26" s="8" t="n">
+      <c r="N26" s="7" t="n">
         <v>1.595</v>
       </c>
-      <c r="O26" s="8" t="n">
+      <c r="O26" s="7" t="n">
         <v>1.1298</v>
       </c>
-      <c r="P26" s="8" t="n">
+      <c r="P26" s="7" t="n">
         <v>2.3446</v>
       </c>
-      <c r="Q26" s="8" t="n">
+      <c r="Q26" s="7" t="n">
         <v>0.613</v>
       </c>
-      <c r="R26" s="8" t="n">
+      <c r="R26" s="7" t="n">
         <v>0.9286</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="7" t="n">
         <v>3.474</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E27" s="7" t="n">
         <v>1.568</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="7" t="n">
         <v>1.0147</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="G27" s="7" t="n">
         <v>2.3944</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="7" t="n">
         <v>0.5888</v>
       </c>
-      <c r="I27" s="8" t="n">
+      <c r="I27" s="7" t="n">
         <v>0.8627</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="L27" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="7" t="n">
         <v>3.1558</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="7" t="n">
         <v>1.595</v>
       </c>
-      <c r="O27" s="8" t="n">
+      <c r="O27" s="7" t="n">
         <v>1.1298</v>
       </c>
-      <c r="P27" s="8" t="n">
+      <c r="P27" s="7" t="n">
         <v>2.3446</v>
       </c>
-      <c r="Q27" s="8" t="n">
+      <c r="Q27" s="7" t="n">
         <v>0.613</v>
       </c>
-      <c r="R27" s="8" t="n">
+      <c r="R27" s="7" t="n">
         <v>0.9286</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="7" t="n">
         <v>3.1228</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="7" t="n">
         <v>1.1475</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F28" s="7" t="n">
         <v>0.7108</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G28" s="7" t="n">
         <v>1.8335</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="7" t="n">
         <v>0.5485</v>
       </c>
-      <c r="I28" s="8" t="n">
+      <c r="I28" s="7" t="n">
         <v>0.752</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="L28" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="7" t="n">
         <v>3.4033</v>
       </c>
-      <c r="N28" s="8" t="n">
+      <c r="N28" s="7" t="n">
         <v>1.4658</v>
       </c>
-      <c r="O28" s="8" t="n">
+      <c r="O28" s="7" t="n">
         <v>0.815</v>
       </c>
-      <c r="P28" s="8" t="n">
+      <c r="P28" s="7" t="n">
         <v>2.3835</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="Q28" s="7" t="n">
         <v>0.541</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="7" t="n">
         <v>0.8455</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D29" s="7" t="n">
         <v>3.7744</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E29" s="7" t="n">
         <v>1.5158</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F29" s="7" t="n">
         <v>0.9572</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G29" s="7" t="n">
         <v>2.5386</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="7" t="n">
         <v>0.5404</v>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I29" s="7" t="n">
         <v>0.8327</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="L29" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="7" t="n">
         <v>3.0659</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="N29" s="7" t="n">
         <v>1.3233</v>
       </c>
-      <c r="O29" s="8" t="n">
+      <c r="O29" s="7" t="n">
         <v>0.8964</v>
       </c>
-      <c r="P29" s="8" t="n">
+      <c r="P29" s="7" t="n">
         <v>2.0002</v>
       </c>
-      <c r="Q29" s="8" t="n">
+      <c r="Q29" s="7" t="n">
         <v>0.5215</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="7" t="n">
         <v>0.7756</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D30" s="8" t="n">
+      <c r="D30" s="7" t="n">
         <v>2.9078</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="7" t="n">
         <v>1.2282</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="7" t="n">
         <v>0.8033</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="G30" s="7" t="n">
         <v>1.9146</v>
       </c>
-      <c r="H30" s="8" t="n">
+      <c r="H30" s="7" t="n">
         <v>0.4885</v>
       </c>
-      <c r="I30" s="8" t="n">
+      <c r="I30" s="7" t="n">
         <v>0.7563</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L30" s="7" t="s">
+      <c r="L30" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="M30" s="7" t="n">
         <v>2.9487</v>
       </c>
-      <c r="N30" s="8" t="n">
+      <c r="N30" s="7" t="n">
         <v>1.4064</v>
       </c>
-      <c r="O30" s="8" t="n">
+      <c r="O30" s="7" t="n">
         <v>0.8933</v>
       </c>
-      <c r="P30" s="8" t="n">
+      <c r="P30" s="7" t="n">
         <v>2.0781</v>
       </c>
-      <c r="Q30" s="8" t="n">
+      <c r="Q30" s="7" t="n">
         <v>0.5917</v>
       </c>
-      <c r="R30" s="8" t="n">
+      <c r="R30" s="7" t="n">
         <v>0.816</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D31" s="7" t="n">
         <v>2.9493</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E31" s="7" t="n">
         <v>1.3057</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="7" t="n">
         <v>0.7483</v>
       </c>
-      <c r="G31" s="8" t="n">
+      <c r="G31" s="7" t="n">
         <v>1.731</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="7" t="n">
         <v>0.5227</v>
       </c>
-      <c r="I31" s="8" t="n">
+      <c r="I31" s="7" t="n">
         <v>0.744</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="L31" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="7" t="n">
         <v>2.6146</v>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="N31" s="7" t="n">
         <v>1.2315</v>
       </c>
-      <c r="O31" s="8" t="n">
+      <c r="O31" s="7" t="n">
         <v>0.8891</v>
       </c>
-      <c r="P31" s="8" t="n">
+      <c r="P31" s="7" t="n">
         <v>1.5082</v>
       </c>
-      <c r="Q31" s="8" t="n">
+      <c r="Q31" s="7" t="n">
         <v>0.562</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="7" t="n">
         <v>0.7938</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="7" t="n">
         <v>2.9493</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="7" t="n">
         <v>1.3057</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="7" t="n">
         <v>0.7483</v>
       </c>
-      <c r="G32" s="8" t="n">
+      <c r="G32" s="7" t="n">
         <v>1.731</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="7" t="n">
         <v>0.5227</v>
       </c>
-      <c r="I32" s="8" t="n">
+      <c r="I32" s="7" t="n">
         <v>0.744</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="K32" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="L32" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="7" t="n">
         <v>3.0223</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="7" t="n">
         <v>1.2343</v>
       </c>
-      <c r="O32" s="8" t="n">
+      <c r="O32" s="7" t="n">
         <v>0.8509</v>
       </c>
-      <c r="P32" s="8" t="n">
+      <c r="P32" s="7" t="n">
         <v>1.9073</v>
       </c>
-      <c r="Q32" s="8" t="n">
+      <c r="Q32" s="7" t="n">
         <v>0.6009</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="7" t="n">
         <v>0.7895</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="7" t="n">
         <v>3.0836</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="E33" s="7" t="n">
         <v>1.3978</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="7" t="n">
         <v>0.7564</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="7" t="n">
         <v>2.128</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="7" t="n">
         <v>0.5662</v>
       </c>
-      <c r="I33" s="8" t="n">
+      <c r="I33" s="7" t="n">
         <v>0.8238</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K33" s="6" t="s">
+      <c r="K33" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L33" s="7" t="s">
+      <c r="L33" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="7" t="n">
         <v>3.1513</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="7" t="n">
         <v>1.423</v>
       </c>
-      <c r="O33" s="8" t="n">
+      <c r="O33" s="7" t="n">
         <v>0.8362</v>
       </c>
-      <c r="P33" s="8" t="n">
+      <c r="P33" s="7" t="n">
         <v>1.8719</v>
       </c>
-      <c r="Q33" s="8" t="n">
+      <c r="Q33" s="7" t="n">
         <v>0.5218</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="7" t="n">
         <v>0.8316</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="D34" s="8" t="n">
+      <c r="D34" s="7" t="n">
         <v>2.9487</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="7" t="n">
         <v>1.4064</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="7" t="n">
         <v>0.8933</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="7" t="n">
         <v>2.0781</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="7" t="n">
         <v>0.5917</v>
       </c>
-      <c r="I34" s="8" t="n">
+      <c r="I34" s="7" t="n">
         <v>0.816</v>
       </c>
-      <c r="J34" s="6" t="s">
+      <c r="J34" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L34" s="7" t="s">
+      <c r="L34" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="7" t="n">
         <v>2.4802</v>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="N34" s="7" t="n">
         <v>1.1618</v>
       </c>
-      <c r="O34" s="8" t="n">
+      <c r="O34" s="7" t="n">
         <v>0.7786</v>
       </c>
-      <c r="P34" s="8" t="n">
+      <c r="P34" s="7" t="n">
         <v>1.727</v>
       </c>
-      <c r="Q34" s="8" t="n">
+      <c r="Q34" s="7" t="n">
         <v>0.4818</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="7" t="n">
         <v>0.7314</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="D35" s="8" t="n">
+      <c r="D35" s="7" t="n">
         <v>3.0696</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="7" t="n">
         <v>1.329</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="7" t="n">
         <v>0.9177</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="7" t="n">
         <v>2.0616</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="7" t="n">
         <v>0.519</v>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="I35" s="7" t="n">
         <v>0.8284</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="J35" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K35" s="6" t="s">
+      <c r="K35" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L35" s="7" t="s">
+      <c r="L35" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="7" t="n">
         <v>2.7204</v>
       </c>
-      <c r="N35" s="8" t="n">
+      <c r="N35" s="7" t="n">
         <v>1.3771</v>
       </c>
-      <c r="O35" s="8" t="n">
+      <c r="O35" s="7" t="n">
         <v>0.8784</v>
       </c>
-      <c r="P35" s="8" t="n">
+      <c r="P35" s="7" t="n">
         <v>1.8606</v>
       </c>
-      <c r="Q35" s="8" t="n">
+      <c r="Q35" s="7" t="n">
         <v>0.5085</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="7" t="n">
         <v>0.7159</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="7" t="n">
         <v>3.0988</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="7" t="n">
         <v>1.2703</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="7" t="n">
         <v>0.8775</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="7" t="n">
         <v>2.228</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="7" t="n">
         <v>0.5048</v>
       </c>
-      <c r="I36" s="8" t="n">
+      <c r="I36" s="7" t="n">
         <v>0.8005</v>
       </c>
-      <c r="J36" s="6" t="s">
+      <c r="J36" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L36" s="10" t="s">
+      <c r="L36" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="7" t="n">
         <v>2.593</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="7" t="n">
         <v>1.458</v>
       </c>
-      <c r="O36" s="8" t="n">
+      <c r="O36" s="7" t="n">
         <v>0.9993</v>
       </c>
-      <c r="P36" s="8" t="n">
+      <c r="P36" s="7" t="n">
         <v>1.0525</v>
       </c>
-      <c r="Q36" s="8" t="n">
+      <c r="Q36" s="7" t="n">
         <v>0.5637</v>
       </c>
-      <c r="R36" s="8" t="n">
+      <c r="R36" s="7" t="n">
         <v>0.7763</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D37" s="8" t="n">
+      <c r="D37" s="7" t="n">
         <v>2.5893</v>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="E37" s="7" t="n">
         <v>1.383</v>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="7" t="n">
         <v>1.0193</v>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="G37" s="7" t="n">
         <v>2.0898</v>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="H37" s="7" t="n">
         <v>0.6343</v>
       </c>
-      <c r="I37" s="8" t="n">
+      <c r="I37" s="7" t="n">
         <v>0.7883</v>
       </c>
-      <c r="J37" s="6" t="s">
+      <c r="J37" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K37" s="6" t="s">
+      <c r="K37" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" s="7" t="n">
         <v>3.3518</v>
       </c>
-      <c r="N37" s="8" t="n">
+      <c r="N37" s="7" t="n">
         <v>1.47</v>
       </c>
-      <c r="O37" s="8" t="n">
+      <c r="O37" s="7" t="n">
         <v>0.9073</v>
       </c>
-      <c r="P37" s="8" t="n">
+      <c r="P37" s="7" t="n">
         <v>2.2588</v>
       </c>
-      <c r="Q37" s="8" t="n">
+      <c r="Q37" s="7" t="n">
         <v>0.563</v>
       </c>
-      <c r="R37" s="8" t="n">
+      <c r="R37" s="7" t="n">
         <v>0.895</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="7" t="n">
         <v>2.5893</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="7" t="n">
         <v>1.383</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="7" t="n">
         <v>1.0193</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G38" s="7" t="n">
         <v>2.0898</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H38" s="7" t="n">
         <v>0.6343</v>
       </c>
-      <c r="I38" s="8" t="n">
+      <c r="I38" s="7" t="n">
         <v>0.7883</v>
       </c>
-      <c r="J38" s="6" t="s">
+      <c r="J38" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L38" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="7" t="n">
         <v>2.24</v>
       </c>
-      <c r="N38" s="8" t="n">
+      <c r="N38" s="7" t="n">
         <v>1.209</v>
       </c>
-      <c r="O38" s="8" t="n">
+      <c r="O38" s="7" t="n">
         <v>0.837</v>
       </c>
-      <c r="P38" s="8" t="n">
+      <c r="P38" s="7" t="n">
         <v>1.7855</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="7" t="n">
         <v>0.4885</v>
       </c>
-      <c r="R38" s="8" t="n">
+      <c r="R38" s="7" t="n">
         <v>0.753</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D39" s="8" t="n">
+      <c r="D39" s="7" t="n">
         <v>2.24</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="E39" s="7" t="n">
         <v>1.209</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="7" t="n">
         <v>0.837</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G39" s="7" t="n">
         <v>1.7855</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="7" t="n">
         <v>0.4885</v>
       </c>
-      <c r="I39" s="8" t="n">
+      <c r="I39" s="7" t="n">
         <v>0.753</v>
       </c>
-      <c r="J39" s="6" t="s">
+      <c r="J39" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="K39" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L39" s="9" t="s">
+      <c r="L39" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="7" t="n">
         <v>3.6232</v>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="7" t="n">
         <v>1.5946</v>
       </c>
-      <c r="O39" s="8" t="n">
+      <c r="O39" s="7" t="n">
         <v>1.0584</v>
       </c>
-      <c r="P39" s="8" t="n">
+      <c r="P39" s="7" t="n">
         <v>2.1651</v>
       </c>
-      <c r="Q39" s="8" t="n">
+      <c r="Q39" s="7" t="n">
         <v>0.6704</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="R39" s="7" t="n">
         <v>1.0121</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D40" s="7" t="n">
         <v>2.4653</v>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="7" t="n">
         <v>1.091</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="7" t="n">
         <v>0.7012</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G40" s="7" t="n">
         <v>1.633</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="7" t="n">
         <v>0.4758</v>
       </c>
-      <c r="I40" s="8" t="n">
+      <c r="I40" s="7" t="n">
         <v>0.6512</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L40" s="9" t="s">
+      <c r="L40" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" s="7" t="n">
         <v>2.4498</v>
       </c>
-      <c r="N40" s="8" t="n">
+      <c r="N40" s="7" t="n">
         <v>1.3392</v>
       </c>
-      <c r="O40" s="8" t="n">
+      <c r="O40" s="7" t="n">
         <v>0.679</v>
       </c>
-      <c r="P40" s="8" t="n">
+      <c r="P40" s="7" t="n">
         <v>1.459</v>
       </c>
-      <c r="Q40" s="8" t="n">
+      <c r="Q40" s="7" t="n">
         <v>0.4752</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="7" t="n">
         <v>0.6936</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="D41" s="8" t="n">
+      <c r="D41" s="7" t="n">
         <v>2.4653</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="E41" s="7" t="n">
         <v>1.091</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="7" t="n">
         <v>0.7012</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G41" s="7" t="n">
         <v>1.633</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="7" t="n">
         <v>0.4758</v>
       </c>
-      <c r="I41" s="8" t="n">
+      <c r="I41" s="7" t="n">
         <v>0.6512</v>
       </c>
-      <c r="J41" s="6" t="s">
+      <c r="J41" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="L41" s="9" t="s">
+      <c r="L41" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M41" s="7" t="n">
         <v>2.4365</v>
       </c>
-      <c r="N41" s="8" t="n">
+      <c r="N41" s="7" t="n">
         <v>1.3663</v>
       </c>
-      <c r="O41" s="8" t="n">
+      <c r="O41" s="7" t="n">
         <v>0.8631</v>
       </c>
-      <c r="P41" s="8" t="n">
+      <c r="P41" s="7" t="n">
         <v>2.1103</v>
       </c>
-      <c r="Q41" s="8" t="n">
+      <c r="Q41" s="7" t="n">
         <v>0.4787</v>
       </c>
-      <c r="R41" s="8" t="n">
+      <c r="R41" s="7" t="n">
         <v>0.7742</v>
       </c>
     </row>
@@ -38852,4 +38543,4173 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C94"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="23.65"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>7.65418769269698</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>4.75976943551409</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>5.3392646109202</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>2.63950335385402</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>2.2737869076063</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>9.31384712574605</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>4.54843268034394</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>6.69659450307191</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>5.1880569173094</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>7.58918163519844</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>7.13487470311756</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>5.04793930836235</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>5.55391330451108</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>0.393359810466168</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>4.54769166225586</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>4.01472123691835</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>4.87764500055603</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>4.64028291454224</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>3.98107042518447</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>4.94958585548051</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>3.89849605343983</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>5.5665942219109</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>3.01201267931669</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>17.8991095023056</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>19.8480983778081</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>19.6904888340597</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>23.2485797459577</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>19.2244841631936</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>16.591192053765</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>18.9772980773588</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>17.6295605065813</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>19.6953513574126</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>17.4076673253417</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>25.0031102815127</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>18.8042326904947</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>13.8735354622129</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>19.8716010009508</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>19.4261904348943</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>21.3973373310459</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>18.2129763459584</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>19.4257296047073</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>17.380171184869</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>20.7210883140512</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>19.4017324659828</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>19.7815325367355</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>18.8887910042718</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>23.4838742742685</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>21.4627101204435</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>20.0768458187763</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>39.5354423919886</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>40.8976661687444</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>40.0967055012545</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>38.1467719175782</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>41.8813415438641</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>39.6903305463533</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>36.025637536351</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>42.0668344135397</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>42.2775118889051</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>38.4938113689585</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>41.4068097788477</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>42.5900304412503</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>36.8374701826561</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C83" s="11" t="n">
+        <v>41.9876265945101</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>38.7244462358871</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C85" s="11" t="n">
+        <v>41.0016913926611</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>40.5511178657678</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>39.407946888182</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>38.5779797714872</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C89" s="11" t="n">
+        <v>42.9519279648274</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>44.4378216660649</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C91" s="11" t="n">
+        <v>40.4423702943444</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>39.7878632148714</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C93" s="11" t="n">
+        <v>43.4638115395331</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>40.854486457966</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D221"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C40" s="0" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C41" s="0" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C42" s="0" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" s="0" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C44" s="0" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C45" s="0" t="n">
+        <v>26.51</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C49" s="0" t="n">
+        <v>23.96</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="0" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C51" s="0" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C52" s="0" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C53" s="0" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C54" s="0" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C55" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C56" s="0" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C57" s="0" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="D57" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" s="0" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C59" s="0" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="D64" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="D65" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C66" s="0" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="D66" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C67" s="0" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C68" s="0" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C69" s="0" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="D71" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C75" s="0" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="D75" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C76" s="0" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="D76" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" s="0" t="n">
+        <v>22.32</v>
+      </c>
+      <c r="D77" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C78" s="0" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C79" s="0" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C80" s="0" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C81" s="0" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="D81" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C82" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D82" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C84" s="0" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="D84" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C85" s="0" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="D85" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C86" s="0" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="D86" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C87" s="0" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="D87" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C88" s="0" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D88" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C89" s="0" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="D89" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C90" s="0" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="D90" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C91" s="0" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="D91" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C92" s="0" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="D92" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C93" s="0" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="D93" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C94" s="0" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="D94" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C95" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D95" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C96" s="0" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="D96" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C97" s="0" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C98" s="0" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C99" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C100" s="0" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C101" s="0" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C102" s="0" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="D102" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C103" s="0" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="D103" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C104" s="0" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C105" s="0" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C106" s="0" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C107" s="0" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C108" s="0" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="D108" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C109" s="0" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="D109" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C110" s="0" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C111" s="0" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C112" s="0" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="D112" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C113" s="0" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="D113" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C114" s="0" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C115" s="0" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C116" s="0" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C117" s="0" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C118" s="0" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="D118" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C119" s="0" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="D119" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C120" s="0" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C121" s="0" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C122" s="0" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C123" s="0" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C124" s="0" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C125" s="0" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C126" s="0" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="D126" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C127" s="0" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B128" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C128" s="0" t="n">
+        <v>23.92</v>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B129" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C129" s="0" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="D129" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C130" s="0" t="n">
+        <v>24.18</v>
+      </c>
+      <c r="D130" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C131" s="0" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="D131" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B132" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C132" s="0" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="D132" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B133" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C133" s="0" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="D133" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B134" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C134" s="0" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="D134" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B135" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C135" s="0" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="D135" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B136" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C136" s="0" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="D136" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B137" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C137" s="0" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="D137" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B138" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C138" s="0" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="D138" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B139" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C139" s="0" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="D139" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B140" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C140" s="0" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="D140" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B141" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C141" s="0" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="D141" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B142" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C142" s="0" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="D142" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B143" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C143" s="0" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="D143" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C144" s="0" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="D144" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C145" s="0" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="D145" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B146" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C146" s="0" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="D146" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B147" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C147" s="0" t="n">
+        <v>27.28</v>
+      </c>
+      <c r="D147" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C148" s="0" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="D148" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C149" s="0" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="D149" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C150" s="0" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="D150" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C151" s="0" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="D151" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C152" s="0" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="D152" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C153" s="0" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="D153" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B154" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C154" s="0" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="D154" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B155" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C155" s="0" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="D155" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B156" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C156" s="0" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="D156" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B157" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C157" s="0" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="D157" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B158" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C158" s="0" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="D158" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B159" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C159" s="0" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D159" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B160" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C160" s="0" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D160" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B161" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C161" s="0" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="D161" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B162" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C162" s="0" t="n">
+        <v>26.22</v>
+      </c>
+      <c r="D162" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B163" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C163" s="0" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="D163" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B164" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C164" s="0" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D164" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B165" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C165" s="0" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="D165" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B166" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C166" s="0" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="D166" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B167" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C167" s="0" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="D167" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B168" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C168" s="0" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="D168" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B169" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C169" s="0" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="D169" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B170" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C170" s="0" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="D170" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B171" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C171" s="0" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="D171" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B172" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C172" s="0" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="D172" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B173" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C173" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D173" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B174" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C174" s="0" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="D174" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B175" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C175" s="0" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="D175" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B176" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C176" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D176" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B177" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C177" s="0" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="D177" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B178" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C178" s="0" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="D178" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B179" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C179" s="0" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="D179" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B180" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C180" s="0" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="D180" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B181" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C181" s="0" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="D181" s="0" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B182" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C182" s="0" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="D182" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B183" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C183" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D183" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B184" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C184" s="0" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="D184" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B185" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C185" s="0" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D185" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B186" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C186" s="0" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="D186" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B187" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C187" s="0" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="D187" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B188" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C188" s="0" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="D188" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B189" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C189" s="0" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="D189" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B190" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C190" s="0" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="D190" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B191" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C191" s="0" t="n">
+        <v>24.27</v>
+      </c>
+      <c r="D191" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B192" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C192" s="0" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="D192" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B193" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C193" s="0" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="D193" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B194" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C194" s="0" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="D194" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B195" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C195" s="0" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="D195" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B196" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C196" s="0" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="D196" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B197" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C197" s="0" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="D197" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B198" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C198" s="0" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="D198" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B199" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C199" s="0" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="D199" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B200" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C200" s="0" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="D200" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B201" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C201" s="0" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="D201" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B202" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C202" s="0" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="D202" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B203" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C203" s="0" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="D203" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B204" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C204" s="0" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="D204" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B205" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C205" s="0" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="D205" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B206" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C206" s="0" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="D206" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B207" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C207" s="0" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="D207" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B208" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C208" s="0" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="D208" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B209" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C209" s="0" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="D209" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B210" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C210" s="0" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="D210" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B211" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C211" s="0" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="D211" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B212" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C212" s="0" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="D212" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B213" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C213" s="0" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="D213" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B214" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C214" s="0" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="D214" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B215" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C215" s="0" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="D215" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B216" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C216" s="0" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="D216" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B217" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C217" s="0" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="D217" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B218" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C218" s="0" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="D218" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B219" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C219" s="0" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="D219" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B220" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C220" s="0" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="D220" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B221" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="C221" s="0" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="D221" s="0" t="n">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/linearmodels/next_steps_data.xlsx
+++ b/linearmodels/next_steps_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="sdrp_birds" sheetId="1" state="visible" r:id="rId3"/>
@@ -1006,7 +1006,7 @@
     <t xml:space="preserve">Likert</t>
   </si>
   <si>
-    <t xml:space="preserve">Distance category</t>
+    <t xml:space="preserve">Distance.category</t>
   </si>
   <si>
     <t xml:space="preserve">Distance</t>
@@ -39610,3096 +39610,3096 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="11" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="11" t="n">
         <v>30.3</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="11" t="n">
         <v>27.28</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="11" t="n">
         <v>29.95</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="11" t="n">
         <v>29.41</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="11" t="n">
         <v>27.63</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="11" t="n">
         <v>29.61</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="11" t="n">
         <v>26.84</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="11" t="n">
         <v>25.28</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="0" t="s">
+      <c r="A10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="11" t="n">
         <v>28.34</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="11" t="n">
         <v>28.76</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="11" t="n">
         <v>24.17</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="11" t="n">
         <v>25.17</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="11" t="n">
         <v>25.56</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="11" t="n">
         <v>22.15</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="11" t="n">
         <v>25.53</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="0" t="s">
+      <c r="A17" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="11" t="n">
         <v>23.16</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="0" t="s">
+      <c r="A18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="11" t="n">
         <v>24.67</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="11" t="n">
         <v>25.19</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="11" t="n">
         <v>21.11</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="11" t="n">
         <v>25.89</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="11" t="n">
         <v>29.12</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="D22" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="11" t="n">
         <v>29.13</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="11" t="n">
         <v>27.85</v>
       </c>
-      <c r="D25" s="0" t="n">
+      <c r="D25" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="11" t="n">
         <v>27.16</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="11" t="n">
         <v>28.14</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="11" t="n">
         <v>24.56</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="0" t="s">
+      <c r="A30" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="11" t="n">
         <v>28.73</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D30" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="11" t="n">
         <v>27.93</v>
       </c>
-      <c r="D31" s="0" t="n">
+      <c r="D31" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="11" t="n">
         <v>27.43</v>
       </c>
-      <c r="D32" s="0" t="n">
+      <c r="D32" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="11" t="n">
         <v>22.78</v>
       </c>
-      <c r="D33" s="0" t="n">
+      <c r="D33" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="11" t="n">
         <v>23.53</v>
       </c>
-      <c r="D34" s="0" t="n">
+      <c r="D34" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="A35" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="11" t="n">
         <v>24.02</v>
       </c>
-      <c r="D35" s="0" t="n">
+      <c r="D35" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="11" t="n">
         <v>20.51</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B37" s="0" t="s">
+      <c r="A37" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="11" t="n">
         <v>24.08</v>
       </c>
-      <c r="D37" s="0" t="n">
+      <c r="D37" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B38" s="0" t="s">
+      <c r="A38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="D38" s="0" t="n">
+      <c r="D38" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="11" t="n">
         <v>20.76</v>
       </c>
-      <c r="D39" s="0" t="n">
+      <c r="D39" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="11" t="n">
         <v>23.1</v>
       </c>
-      <c r="D40" s="0" t="n">
+      <c r="D40" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41" s="11" t="n">
         <v>19.31</v>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D41" s="11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C42" s="0" t="n">
+      <c r="C42" s="11" t="n">
         <v>27.63</v>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C43" s="0" t="n">
+      <c r="C43" s="11" t="n">
         <v>24.95</v>
       </c>
-      <c r="D43" s="0" t="n">
+      <c r="D43" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="A44" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="11" t="n">
         <v>27.63</v>
       </c>
-      <c r="D44" s="0" t="n">
+      <c r="D44" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C45" s="0" t="n">
+      <c r="C45" s="11" t="n">
         <v>26.51</v>
       </c>
-      <c r="D45" s="0" t="n">
+      <c r="D45" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="A46" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C46" s="0" t="n">
+      <c r="C46" s="11" t="n">
         <v>26.02</v>
       </c>
-      <c r="D46" s="0" t="n">
+      <c r="D46" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="A47" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C47" s="0" t="n">
+      <c r="C47" s="11" t="n">
         <v>27.77</v>
       </c>
-      <c r="D47" s="0" t="n">
+      <c r="D47" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48" s="11" t="n">
         <v>25.38</v>
       </c>
-      <c r="D48" s="0" t="n">
+      <c r="D48" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="A49" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C49" s="0" t="n">
+      <c r="C49" s="11" t="n">
         <v>23.96</v>
       </c>
-      <c r="D49" s="0" t="n">
+      <c r="D49" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" s="0" t="s">
+      <c r="A50" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="11" t="n">
         <v>25.81</v>
       </c>
-      <c r="D50" s="0" t="n">
+      <c r="D50" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="11" t="n">
         <v>26.89</v>
       </c>
-      <c r="D51" s="0" t="n">
+      <c r="D51" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="11" t="n">
         <v>25.89</v>
       </c>
-      <c r="D52" s="0" t="n">
+      <c r="D52" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
+      <c r="A53" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="11" t="n">
         <v>21.85</v>
       </c>
-      <c r="D53" s="0" t="n">
+      <c r="D53" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+      <c r="A54" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="0" t="n">
+      <c r="C54" s="11" t="n">
         <v>22.58</v>
       </c>
-      <c r="D54" s="0" t="n">
+      <c r="D54" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
+      <c r="A55" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C55" s="0" t="n">
+      <c r="C55" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="D55" s="0" t="n">
+      <c r="D55" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
+      <c r="A56" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56" s="11" t="n">
         <v>19.43</v>
       </c>
-      <c r="D56" s="0" t="n">
+      <c r="D56" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="0" t="s">
+      <c r="A57" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C57" s="0" t="n">
+      <c r="C57" s="11" t="n">
         <v>23.42</v>
       </c>
-      <c r="D57" s="0" t="n">
+      <c r="D57" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B58" s="0" t="s">
+      <c r="A58" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C58" s="0" t="n">
+      <c r="C58" s="11" t="n">
         <v>21.22</v>
       </c>
-      <c r="D58" s="0" t="n">
+      <c r="D58" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="n">
+      <c r="A59" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C59" s="0" t="n">
+      <c r="C59" s="11" t="n">
         <v>19.26</v>
       </c>
-      <c r="D59" s="0" t="n">
+      <c r="D59" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="n">
+      <c r="A60" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C60" s="0" t="n">
+      <c r="C60" s="11" t="n">
         <v>22.23</v>
       </c>
-      <c r="D60" s="0" t="n">
+      <c r="D60" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="n">
+      <c r="A61" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C61" s="0" t="n">
+      <c r="C61" s="11" t="n">
         <v>18.82</v>
       </c>
-      <c r="D61" s="0" t="n">
+      <c r="D61" s="11" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="n">
+      <c r="A62" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C62" s="0" t="n">
+      <c r="C62" s="11" t="n">
         <v>27.39</v>
       </c>
-      <c r="D62" s="0" t="n">
+      <c r="D62" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="n">
+      <c r="A63" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C63" s="0" t="n">
+      <c r="C63" s="11" t="n">
         <v>23.67</v>
       </c>
-      <c r="D63" s="0" t="n">
+      <c r="D63" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="n">
+      <c r="A64" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C64" s="0" t="n">
+      <c r="C64" s="11" t="n">
         <v>27.21</v>
       </c>
-      <c r="D64" s="0" t="n">
+      <c r="D64" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="n">
+      <c r="A65" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C65" s="0" t="n">
+      <c r="C65" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="D65" s="0" t="n">
+      <c r="D65" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="n">
+      <c r="A66" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C66" s="0" t="n">
+      <c r="C66" s="11" t="n">
         <v>25.98</v>
       </c>
-      <c r="D66" s="0" t="n">
+      <c r="D66" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="n">
+      <c r="A67" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C67" s="0" t="n">
+      <c r="C67" s="11" t="n">
         <v>27.48</v>
       </c>
-      <c r="D67" s="0" t="n">
+      <c r="D67" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="n">
+      <c r="A68" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C68" s="0" t="n">
+      <c r="C68" s="11" t="n">
         <v>25.11</v>
       </c>
-      <c r="D68" s="0" t="n">
+      <c r="D68" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="n">
+      <c r="A69" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C69" s="0" t="n">
+      <c r="C69" s="11" t="n">
         <v>24.18</v>
       </c>
-      <c r="D69" s="0" t="n">
+      <c r="D69" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B70" s="0" t="s">
+      <c r="A70" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B70" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C70" s="0" t="n">
+      <c r="C70" s="11" t="n">
         <v>25.21</v>
       </c>
-      <c r="D70" s="0" t="n">
+      <c r="D70" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="n">
+      <c r="A71" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C71" s="0" t="n">
+      <c r="C71" s="11" t="n">
         <v>26.28</v>
       </c>
-      <c r="D71" s="0" t="n">
+      <c r="D71" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="n">
+      <c r="A72" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C72" s="0" t="n">
+      <c r="C72" s="11" t="n">
         <v>24.78</v>
       </c>
-      <c r="D72" s="0" t="n">
+      <c r="D72" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="n">
+      <c r="A73" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C73" s="0" t="n">
+      <c r="C73" s="11" t="n">
         <v>21.23</v>
       </c>
-      <c r="D73" s="0" t="n">
+      <c r="D73" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="n">
+      <c r="A74" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C74" s="0" t="n">
+      <c r="C74" s="11" t="n">
         <v>21.47</v>
       </c>
-      <c r="D74" s="0" t="n">
+      <c r="D74" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="n">
+      <c r="A75" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C75" s="0" t="n">
+      <c r="C75" s="11" t="n">
         <v>21.57</v>
       </c>
-      <c r="D75" s="0" t="n">
+      <c r="D75" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="n">
+      <c r="A76" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C76" s="0" t="n">
+      <c r="C76" s="11" t="n">
         <v>18.35</v>
       </c>
-      <c r="D76" s="0" t="n">
+      <c r="D76" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B77" s="0" t="s">
+      <c r="A77" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B77" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C77" s="0" t="n">
+      <c r="C77" s="11" t="n">
         <v>22.32</v>
       </c>
-      <c r="D77" s="0" t="n">
+      <c r="D77" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B78" s="0" t="s">
+      <c r="A78" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B78" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C78" s="0" t="n">
+      <c r="C78" s="11" t="n">
         <v>20.62</v>
       </c>
-      <c r="D78" s="0" t="n">
+      <c r="D78" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="n">
+      <c r="A79" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C79" s="0" t="n">
+      <c r="C79" s="11" t="n">
         <v>18.48</v>
       </c>
-      <c r="D79" s="0" t="n">
+      <c r="D79" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="n">
+      <c r="A80" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C80" s="0" t="n">
+      <c r="C80" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="D80" s="0" t="n">
+      <c r="D80" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="n">
+      <c r="A81" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C81" s="0" t="n">
+      <c r="C81" s="11" t="n">
         <v>18.03</v>
       </c>
-      <c r="D81" s="0" t="n">
+      <c r="D81" s="11" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="n">
+      <c r="A82" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C82" s="0" t="n">
+      <c r="C82" s="11" t="n">
         <v>27.4</v>
       </c>
-      <c r="D82" s="0" t="n">
+      <c r="D82" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="n">
+      <c r="A83" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C83" s="0" t="n">
+      <c r="C83" s="11" t="n">
         <v>23.01</v>
       </c>
-      <c r="D83" s="0" t="n">
+      <c r="D83" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="n">
+      <c r="A84" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C84" s="0" t="n">
+      <c r="C84" s="11" t="n">
         <v>27.17</v>
       </c>
-      <c r="D84" s="0" t="n">
+      <c r="D84" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="n">
+      <c r="A85" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C85" s="0" t="n">
+      <c r="C85" s="11" t="n">
         <v>25.44</v>
       </c>
-      <c r="D85" s="0" t="n">
+      <c r="D85" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="n">
+      <c r="A86" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C86" s="0" t="n">
+      <c r="C86" s="11" t="n">
         <v>25.58</v>
       </c>
-      <c r="D86" s="0" t="n">
+      <c r="D86" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="n">
+      <c r="A87" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C87" s="0" t="n">
+      <c r="C87" s="11" t="n">
         <v>27.25</v>
       </c>
-      <c r="D87" s="0" t="n">
+      <c r="D87" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="n">
+      <c r="A88" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C88" s="0" t="n">
+      <c r="C88" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="D88" s="0" t="n">
+      <c r="D88" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="n">
+      <c r="A89" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C89" s="0" t="n">
+      <c r="C89" s="11" t="n">
         <v>23.95</v>
       </c>
-      <c r="D89" s="0" t="n">
+      <c r="D89" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B90" s="0" t="s">
+      <c r="A90" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B90" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C90" s="0" t="n">
+      <c r="C90" s="11" t="n">
         <v>24.91</v>
       </c>
-      <c r="D90" s="0" t="n">
+      <c r="D90" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="n">
+      <c r="A91" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C91" s="0" t="n">
+      <c r="C91" s="11" t="n">
         <v>25.98</v>
       </c>
-      <c r="D91" s="0" t="n">
+      <c r="D91" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="n">
+      <c r="A92" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C92" s="0" t="n">
+      <c r="C92" s="11" t="n">
         <v>23.98</v>
       </c>
-      <c r="D92" s="0" t="n">
+      <c r="D92" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="n">
+      <c r="A93" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C93" s="0" t="n">
+      <c r="C93" s="11" t="n">
         <v>20.43</v>
       </c>
-      <c r="D93" s="0" t="n">
+      <c r="D93" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="n">
+      <c r="A94" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C94" s="0" t="n">
+      <c r="C94" s="11" t="n">
         <v>20.35</v>
       </c>
-      <c r="D94" s="0" t="n">
+      <c r="D94" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="n">
+      <c r="A95" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C95" s="0" t="n">
+      <c r="C95" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="D95" s="0" t="n">
+      <c r="D95" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="n">
+      <c r="A96" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C96" s="0" t="n">
+      <c r="C96" s="11" t="n">
         <v>17.61</v>
       </c>
-      <c r="D96" s="0" t="n">
+      <c r="D96" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B97" s="0" t="s">
+      <c r="A97" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C97" s="0" t="n">
+      <c r="C97" s="11" t="n">
         <v>21.29</v>
       </c>
-      <c r="D97" s="0" t="n">
+      <c r="D97" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B98" s="0" t="s">
+      <c r="A98" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B98" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C98" s="0" t="n">
+      <c r="C98" s="11" t="n">
         <v>19.68</v>
       </c>
-      <c r="D98" s="0" t="n">
+      <c r="D98" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="n">
+      <c r="A99" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C99" s="0" t="n">
+      <c r="C99" s="11" t="n">
         <v>17.7</v>
       </c>
-      <c r="D99" s="0" t="n">
+      <c r="D99" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="n">
+      <c r="A100" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C100" s="0" t="n">
+      <c r="C100" s="11" t="n">
         <v>20.52</v>
       </c>
-      <c r="D100" s="0" t="n">
+      <c r="D100" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="n">
+      <c r="A101" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C101" s="0" t="n">
+      <c r="C101" s="11" t="n">
         <v>17.54</v>
       </c>
-      <c r="D101" s="0" t="n">
+      <c r="D101" s="11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="n">
+      <c r="A102" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C102" s="0" t="n">
+      <c r="C102" s="11" t="n">
         <v>27.49</v>
       </c>
-      <c r="D102" s="0" t="n">
+      <c r="D102" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="n">
+      <c r="A103" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C103" s="0" t="n">
+      <c r="C103" s="11" t="n">
         <v>22.13</v>
       </c>
-      <c r="D103" s="0" t="n">
+      <c r="D103" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="n">
+      <c r="A104" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C104" s="0" t="n">
+      <c r="C104" s="11" t="n">
         <v>26.47</v>
       </c>
-      <c r="D104" s="0" t="n">
+      <c r="D104" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="n">
+      <c r="A105" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C105" s="0" t="n">
+      <c r="C105" s="11" t="n">
         <v>24.76</v>
       </c>
-      <c r="D105" s="0" t="n">
+      <c r="D105" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="n">
+      <c r="A106" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C106" s="0" t="n">
+      <c r="C106" s="11" t="n">
         <v>25.76</v>
       </c>
-      <c r="D106" s="0" t="n">
+      <c r="D106" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="n">
+      <c r="A107" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C107" s="0" t="n">
+      <c r="C107" s="11" t="n">
         <v>27.14</v>
       </c>
-      <c r="D107" s="0" t="n">
+      <c r="D107" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="n">
+      <c r="A108" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C108" s="0" t="n">
+      <c r="C108" s="11" t="n">
         <v>25.22</v>
       </c>
-      <c r="D108" s="0" t="n">
+      <c r="D108" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="n">
+      <c r="A109" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C109" s="0" t="n">
+      <c r="C109" s="11" t="n">
         <v>23.53</v>
       </c>
-      <c r="D109" s="0" t="n">
+      <c r="D109" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B110" s="0" t="s">
+      <c r="A110" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B110" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C110" s="0" t="n">
+      <c r="C110" s="11" t="n">
         <v>24.78</v>
       </c>
-      <c r="D110" s="0" t="n">
+      <c r="D110" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="n">
+      <c r="A111" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C111" s="0" t="n">
+      <c r="C111" s="11" t="n">
         <v>25.51</v>
       </c>
-      <c r="D111" s="0" t="n">
+      <c r="D111" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="n">
+      <c r="A112" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C112" s="0" t="n">
+      <c r="C112" s="11" t="n">
         <v>23.01</v>
       </c>
-      <c r="D112" s="0" t="n">
+      <c r="D112" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="n">
+      <c r="A113" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C113" s="0" t="n">
+      <c r="C113" s="11" t="n">
         <v>19.69</v>
       </c>
-      <c r="D113" s="0" t="n">
+      <c r="D113" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="n">
+      <c r="A114" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C114" s="0" t="n">
+      <c r="C114" s="11" t="n">
         <v>19.27</v>
       </c>
-      <c r="D114" s="0" t="n">
+      <c r="D114" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="n">
+      <c r="A115" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C115" s="0" t="n">
+      <c r="C115" s="11" t="n">
         <v>19.87</v>
       </c>
-      <c r="D115" s="0" t="n">
+      <c r="D115" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="n">
+      <c r="A116" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C116" s="0" t="n">
+      <c r="C116" s="11" t="n">
         <v>16.77</v>
       </c>
-      <c r="D116" s="0" t="n">
+      <c r="D116" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B117" s="0" t="s">
+      <c r="A117" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B117" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C117" s="0" t="n">
+      <c r="C117" s="11" t="n">
         <v>20.63</v>
       </c>
-      <c r="D117" s="0" t="n">
+      <c r="D117" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B118" s="0" t="s">
+      <c r="A118" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B118" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C118" s="0" t="n">
+      <c r="C118" s="11" t="n">
         <v>19.19</v>
       </c>
-      <c r="D118" s="0" t="n">
+      <c r="D118" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="n">
+      <c r="A119" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C119" s="0" t="n">
+      <c r="C119" s="11" t="n">
         <v>17.65</v>
       </c>
-      <c r="D119" s="0" t="n">
+      <c r="D119" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="n">
+      <c r="A120" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C120" s="0" t="n">
+      <c r="C120" s="11" t="n">
         <v>19.58</v>
       </c>
-      <c r="D120" s="0" t="n">
+      <c r="D120" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="n">
+      <c r="A121" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C121" s="0" t="n">
+      <c r="C121" s="11" t="n">
         <v>16.66</v>
       </c>
-      <c r="D121" s="0" t="n">
+      <c r="D121" s="11" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="n">
+      <c r="A122" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C122" s="0" t="n">
+      <c r="C122" s="11" t="n">
         <v>26.95</v>
       </c>
-      <c r="D122" s="0" t="n">
+      <c r="D122" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="n">
+      <c r="A123" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C123" s="0" t="n">
+      <c r="C123" s="11" t="n">
         <v>21.26</v>
       </c>
-      <c r="D123" s="0" t="n">
+      <c r="D123" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="n">
+      <c r="A124" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C124" s="0" t="n">
+      <c r="C124" s="11" t="n">
         <v>26.63</v>
       </c>
-      <c r="D124" s="0" t="n">
+      <c r="D124" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="n">
+      <c r="A125" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C125" s="0" t="n">
+      <c r="C125" s="11" t="n">
         <v>24.56</v>
       </c>
-      <c r="D125" s="0" t="n">
+      <c r="D125" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="n">
+      <c r="A126" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C126" s="0" t="n">
+      <c r="C126" s="11" t="n">
         <v>25.49</v>
       </c>
-      <c r="D126" s="0" t="n">
+      <c r="D126" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="n">
+      <c r="A127" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C127" s="0" t="n">
+      <c r="C127" s="11" t="n">
         <v>26.96</v>
       </c>
-      <c r="D127" s="0" t="n">
+      <c r="D127" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="n">
+      <c r="A128" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C128" s="0" t="n">
+      <c r="C128" s="11" t="n">
         <v>23.92</v>
       </c>
-      <c r="D128" s="0" t="n">
+      <c r="D128" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="n">
+      <c r="A129" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C129" s="0" t="n">
+      <c r="C129" s="11" t="n">
         <v>23.57</v>
       </c>
-      <c r="D129" s="0" t="n">
+      <c r="D129" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B130" s="0" t="s">
+      <c r="A130" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B130" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C130" s="0" t="n">
+      <c r="C130" s="11" t="n">
         <v>24.18</v>
       </c>
-      <c r="D130" s="0" t="n">
+      <c r="D130" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="n">
+      <c r="A131" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C131" s="0" t="n">
+      <c r="C131" s="11" t="n">
         <v>25.16</v>
       </c>
-      <c r="D131" s="0" t="n">
+      <c r="D131" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="n">
+      <c r="A132" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C132" s="0" t="n">
+      <c r="C132" s="11" t="n">
         <v>22.16</v>
       </c>
-      <c r="D132" s="0" t="n">
+      <c r="D132" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="n">
+      <c r="A133" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C133" s="0" t="n">
+      <c r="C133" s="11" t="n">
         <v>18.74</v>
       </c>
-      <c r="D133" s="0" t="n">
+      <c r="D133" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="n">
+      <c r="A134" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C134" s="0" t="n">
+      <c r="C134" s="11" t="n">
         <v>18.67</v>
       </c>
-      <c r="D134" s="0" t="n">
+      <c r="D134" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="n">
+      <c r="A135" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C135" s="0" t="n">
+      <c r="C135" s="11" t="n">
         <v>19.46</v>
       </c>
-      <c r="D135" s="0" t="n">
+      <c r="D135" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="n">
+      <c r="A136" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C136" s="0" t="n">
+      <c r="C136" s="11" t="n">
         <v>16.56</v>
       </c>
-      <c r="D136" s="0" t="n">
+      <c r="D136" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B137" s="0" t="s">
+      <c r="A137" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B137" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C137" s="0" t="n">
+      <c r="C137" s="11" t="n">
         <v>19.72</v>
       </c>
-      <c r="D137" s="0" t="n">
+      <c r="D137" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B138" s="0" t="s">
+      <c r="A138" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B138" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C138" s="0" t="n">
+      <c r="C138" s="11" t="n">
         <v>18.87</v>
       </c>
-      <c r="D138" s="0" t="n">
+      <c r="D138" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="n">
+      <c r="A139" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C139" s="0" t="n">
+      <c r="C139" s="11" t="n">
         <v>16.27</v>
       </c>
-      <c r="D139" s="0" t="n">
+      <c r="D139" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="n">
+      <c r="A140" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C140" s="0" t="n">
+      <c r="C140" s="11" t="n">
         <v>18.55</v>
       </c>
-      <c r="D140" s="0" t="n">
+      <c r="D140" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0" t="n">
+      <c r="A141" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B141" s="0" t="s">
+      <c r="B141" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C141" s="0" t="n">
+      <c r="C141" s="11" t="n">
         <v>16.22</v>
       </c>
-      <c r="D141" s="0" t="n">
+      <c r="D141" s="11" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0" t="n">
+      <c r="A142" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B142" s="0" t="s">
+      <c r="B142" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C142" s="0" t="n">
+      <c r="C142" s="11" t="n">
         <v>26.29</v>
       </c>
-      <c r="D142" s="0" t="n">
+      <c r="D142" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="n">
+      <c r="A143" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B143" s="0" t="s">
+      <c r="B143" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C143" s="0" t="n">
+      <c r="C143" s="11" t="n">
         <v>21.28</v>
       </c>
-      <c r="D143" s="0" t="n">
+      <c r="D143" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0" t="n">
+      <c r="A144" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="B144" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C144" s="0" t="n">
+      <c r="C144" s="11" t="n">
         <v>26.35</v>
       </c>
-      <c r="D144" s="0" t="n">
+      <c r="D144" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="0" t="n">
+      <c r="A145" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B145" s="0" t="s">
+      <c r="B145" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C145" s="0" t="n">
+      <c r="C145" s="11" t="n">
         <v>24.12</v>
       </c>
-      <c r="D145" s="0" t="n">
+      <c r="D145" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0" t="n">
+      <c r="A146" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B146" s="0" t="s">
+      <c r="B146" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C146" s="0" t="n">
+      <c r="C146" s="11" t="n">
         <v>25.75</v>
       </c>
-      <c r="D146" s="0" t="n">
+      <c r="D146" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="0" t="n">
+      <c r="A147" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B147" s="0" t="s">
+      <c r="B147" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C147" s="0" t="n">
+      <c r="C147" s="11" t="n">
         <v>27.28</v>
       </c>
-      <c r="D147" s="0" t="n">
+      <c r="D147" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0" t="n">
+      <c r="A148" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B148" s="0" t="s">
+      <c r="B148" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C148" s="0" t="n">
+      <c r="C148" s="11" t="n">
         <v>24.13</v>
       </c>
-      <c r="D148" s="0" t="n">
+      <c r="D148" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0" t="n">
+      <c r="A149" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B149" s="0" t="s">
+      <c r="B149" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C149" s="0" t="n">
+      <c r="C149" s="11" t="n">
         <v>23.85</v>
       </c>
-      <c r="D149" s="0" t="n">
+      <c r="D149" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B150" s="0" t="s">
+      <c r="A150" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B150" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C150" s="0" t="n">
+      <c r="C150" s="11" t="n">
         <v>24.35</v>
       </c>
-      <c r="D150" s="0" t="n">
+      <c r="D150" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="0" t="n">
+      <c r="A151" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B151" s="0" t="s">
+      <c r="B151" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C151" s="0" t="n">
+      <c r="C151" s="11" t="n">
         <v>24.68</v>
       </c>
-      <c r="D151" s="0" t="n">
+      <c r="D151" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="0" t="n">
+      <c r="A152" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B152" s="0" t="s">
+      <c r="B152" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C152" s="0" t="n">
+      <c r="C152" s="11" t="n">
         <v>21.18</v>
       </c>
-      <c r="D152" s="0" t="n">
+      <c r="D152" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="0" t="n">
+      <c r="A153" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B153" s="0" t="s">
+      <c r="B153" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C153" s="0" t="n">
+      <c r="C153" s="11" t="n">
         <v>18.73</v>
       </c>
-      <c r="D153" s="0" t="n">
+      <c r="D153" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="0" t="n">
+      <c r="A154" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B154" s="0" t="s">
+      <c r="B154" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C154" s="0" t="n">
+      <c r="C154" s="11" t="n">
         <v>18.36</v>
       </c>
-      <c r="D154" s="0" t="n">
+      <c r="D154" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="0" t="n">
+      <c r="A155" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B155" s="0" t="s">
+      <c r="B155" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C155" s="0" t="n">
+      <c r="C155" s="11" t="n">
         <v>18.96</v>
       </c>
-      <c r="D155" s="0" t="n">
+      <c r="D155" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="0" t="n">
+      <c r="A156" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B156" s="0" t="s">
+      <c r="B156" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C156" s="0" t="n">
+      <c r="C156" s="11" t="n">
         <v>16.37</v>
       </c>
-      <c r="D156" s="0" t="n">
+      <c r="D156" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B157" s="0" t="s">
+      <c r="A157" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B157" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C157" s="0" t="n">
+      <c r="C157" s="11" t="n">
         <v>19.06</v>
       </c>
-      <c r="D157" s="0" t="n">
+      <c r="D157" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B158" s="0" t="s">
+      <c r="A158" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B158" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C158" s="0" t="n">
+      <c r="C158" s="11" t="n">
         <v>18.54</v>
       </c>
-      <c r="D158" s="0" t="n">
+      <c r="D158" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="0" t="n">
+      <c r="A159" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B159" s="0" t="s">
+      <c r="B159" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C159" s="0" t="n">
+      <c r="C159" s="11" t="n">
         <v>16.07</v>
       </c>
-      <c r="D159" s="0" t="n">
+      <c r="D159" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="0" t="n">
+      <c r="A160" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B160" s="0" t="s">
+      <c r="B160" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C160" s="0" t="n">
+      <c r="C160" s="11" t="n">
         <v>18.29</v>
       </c>
-      <c r="D160" s="0" t="n">
+      <c r="D160" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0" t="n">
+      <c r="A161" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B161" s="0" t="s">
+      <c r="B161" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C161" s="0" t="n">
+      <c r="C161" s="11" t="n">
         <v>15.29</v>
       </c>
-      <c r="D161" s="0" t="n">
+      <c r="D161" s="11" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="0" t="n">
+      <c r="A162" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B162" s="0" t="s">
+      <c r="B162" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C162" s="0" t="n">
+      <c r="C162" s="11" t="n">
         <v>26.22</v>
       </c>
-      <c r="D162" s="0" t="n">
+      <c r="D162" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="0" t="n">
+      <c r="A163" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B163" s="0" t="s">
+      <c r="B163" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C163" s="0" t="n">
+      <c r="C163" s="11" t="n">
         <v>19.41</v>
       </c>
-      <c r="D163" s="0" t="n">
+      <c r="D163" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="0" t="n">
+      <c r="A164" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B164" s="0" t="s">
+      <c r="B164" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C164" s="0" t="n">
+      <c r="C164" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="D164" s="0" t="n">
+      <c r="D164" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="0" t="n">
+      <c r="A165" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B165" s="0" t="s">
+      <c r="B165" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C165" s="0" t="n">
+      <c r="C165" s="11" t="n">
         <v>24.07</v>
       </c>
-      <c r="D165" s="0" t="n">
+      <c r="D165" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="0" t="n">
+      <c r="A166" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B166" s="0" t="s">
+      <c r="B166" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C166" s="0" t="n">
+      <c r="C166" s="11" t="n">
         <v>24.89</v>
       </c>
-      <c r="D166" s="0" t="n">
+      <c r="D166" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="0" t="n">
+      <c r="A167" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B167" s="0" t="s">
+      <c r="B167" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C167" s="0" t="n">
+      <c r="C167" s="11" t="n">
         <v>25.78</v>
       </c>
-      <c r="D167" s="0" t="n">
+      <c r="D167" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="0" t="n">
+      <c r="A168" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B168" s="0" t="s">
+      <c r="B168" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C168" s="0" t="n">
+      <c r="C168" s="11" t="n">
         <v>23.49</v>
       </c>
-      <c r="D168" s="0" t="n">
+      <c r="D168" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="0" t="n">
+      <c r="A169" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B169" s="0" t="s">
+      <c r="B169" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C169" s="0" t="n">
+      <c r="C169" s="11" t="n">
         <v>23.15</v>
       </c>
-      <c r="D169" s="0" t="n">
+      <c r="D169" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B170" s="0" t="s">
+      <c r="A170" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B170" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C170" s="0" t="n">
+      <c r="C170" s="11" t="n">
         <v>23.25</v>
       </c>
-      <c r="D170" s="0" t="n">
+      <c r="D170" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="0" t="n">
+      <c r="A171" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B171" s="0" t="s">
+      <c r="B171" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C171" s="0" t="n">
+      <c r="C171" s="11" t="n">
         <v>24.68</v>
       </c>
-      <c r="D171" s="0" t="n">
+      <c r="D171" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="0" t="n">
+      <c r="A172" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B172" s="0" t="s">
+      <c r="B172" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C172" s="0" t="n">
+      <c r="C172" s="11" t="n">
         <v>20.68</v>
       </c>
-      <c r="D172" s="0" t="n">
+      <c r="D172" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="0" t="n">
+      <c r="A173" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B173" s="0" t="s">
+      <c r="B173" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C173" s="0" t="n">
+      <c r="C173" s="11" t="n">
         <v>17.7</v>
       </c>
-      <c r="D173" s="0" t="n">
+      <c r="D173" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="0" t="n">
+      <c r="A174" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B174" s="0" t="s">
+      <c r="B174" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C174" s="0" t="n">
+      <c r="C174" s="11" t="n">
         <v>16.53</v>
       </c>
-      <c r="D174" s="0" t="n">
+      <c r="D174" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="0" t="n">
+      <c r="A175" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B175" s="0" t="s">
+      <c r="B175" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C175" s="0" t="n">
+      <c r="C175" s="11" t="n">
         <v>17.67</v>
       </c>
-      <c r="D175" s="0" t="n">
+      <c r="D175" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="0" t="n">
+      <c r="A176" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B176" s="0" t="s">
+      <c r="B176" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C176" s="0" t="n">
+      <c r="C176" s="11" t="n">
         <v>14.4</v>
       </c>
-      <c r="D176" s="0" t="n">
+      <c r="D176" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B177" s="0" t="s">
+      <c r="A177" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B177" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C177" s="0" t="n">
+      <c r="C177" s="11" t="n">
         <v>17.42</v>
       </c>
-      <c r="D177" s="0" t="n">
+      <c r="D177" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B178" s="0" t="s">
+      <c r="A178" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B178" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C178" s="0" t="n">
+      <c r="C178" s="11" t="n">
         <v>16.84</v>
       </c>
-      <c r="D178" s="0" t="n">
+      <c r="D178" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="0" t="n">
+      <c r="A179" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B179" s="0" t="s">
+      <c r="B179" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C179" s="0" t="n">
+      <c r="C179" s="11" t="n">
         <v>14.52</v>
       </c>
-      <c r="D179" s="0" t="n">
+      <c r="D179" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="0" t="n">
+      <c r="A180" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B180" s="0" t="s">
+      <c r="B180" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C180" s="0" t="n">
+      <c r="C180" s="11" t="n">
         <v>17.16</v>
       </c>
-      <c r="D180" s="0" t="n">
+      <c r="D180" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="0" t="n">
+      <c r="A181" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B181" s="0" t="s">
+      <c r="B181" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C181" s="0" t="n">
+      <c r="C181" s="11" t="n">
         <v>14.69</v>
       </c>
-      <c r="D181" s="0" t="n">
+      <c r="D181" s="11" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="0" t="n">
+      <c r="A182" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B182" s="0" t="s">
+      <c r="B182" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C182" s="0" t="n">
+      <c r="C182" s="11" t="n">
         <v>25.45</v>
       </c>
-      <c r="D182" s="0" t="n">
+      <c r="D182" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="0" t="n">
+      <c r="A183" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B183" s="0" t="s">
+      <c r="B183" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C183" s="0" t="n">
+      <c r="C183" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="D183" s="0" t="n">
+      <c r="D183" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="0" t="n">
+      <c r="A184" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B184" s="0" t="s">
+      <c r="B184" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C184" s="0" t="n">
+      <c r="C184" s="11" t="n">
         <v>25.16</v>
       </c>
-      <c r="D184" s="0" t="n">
+      <c r="D184" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="0" t="n">
+      <c r="A185" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B185" s="0" t="s">
+      <c r="B185" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C185" s="0" t="n">
+      <c r="C185" s="11" t="n">
         <v>23.5</v>
       </c>
-      <c r="D185" s="0" t="n">
+      <c r="D185" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="0" t="n">
+      <c r="A186" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B186" s="0" t="s">
+      <c r="B186" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C186" s="0" t="n">
+      <c r="C186" s="11" t="n">
         <v>24.56</v>
       </c>
-      <c r="D186" s="0" t="n">
+      <c r="D186" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="0" t="n">
+      <c r="A187" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B187" s="0" t="s">
+      <c r="B187" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C187" s="0" t="n">
+      <c r="C187" s="11" t="n">
         <v>25.53</v>
       </c>
-      <c r="D187" s="0" t="n">
+      <c r="D187" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="0" t="n">
+      <c r="A188" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B188" s="0" t="s">
+      <c r="B188" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C188" s="0" t="n">
+      <c r="C188" s="11" t="n">
         <v>23.21</v>
       </c>
-      <c r="D188" s="0" t="n">
+      <c r="D188" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="0" t="n">
+      <c r="A189" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B189" s="0" t="s">
+      <c r="B189" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C189" s="0" t="n">
+      <c r="C189" s="11" t="n">
         <v>22.42</v>
       </c>
-      <c r="D189" s="0" t="n">
+      <c r="D189" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B190" s="0" t="s">
+      <c r="A190" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B190" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C190" s="0" t="n">
+      <c r="C190" s="11" t="n">
         <v>23.23</v>
       </c>
-      <c r="D190" s="0" t="n">
+      <c r="D190" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="0" t="n">
+      <c r="A191" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B191" s="0" t="s">
+      <c r="B191" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C191" s="0" t="n">
+      <c r="C191" s="11" t="n">
         <v>24.27</v>
       </c>
-      <c r="D191" s="0" t="n">
+      <c r="D191" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="0" t="n">
+      <c r="A192" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B192" s="0" t="s">
+      <c r="B192" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C192" s="0" t="n">
+      <c r="C192" s="11" t="n">
         <v>19.77</v>
       </c>
-      <c r="D192" s="0" t="n">
+      <c r="D192" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="0" t="n">
+      <c r="A193" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B193" s="0" t="s">
+      <c r="B193" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C193" s="0" t="n">
+      <c r="C193" s="11" t="n">
         <v>17.13</v>
       </c>
-      <c r="D193" s="0" t="n">
+      <c r="D193" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="0" t="n">
+      <c r="A194" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B194" s="0" t="s">
+      <c r="B194" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C194" s="0" t="n">
+      <c r="C194" s="11" t="n">
         <v>15.19</v>
       </c>
-      <c r="D194" s="0" t="n">
+      <c r="D194" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="0" t="n">
+      <c r="A195" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B195" s="0" t="s">
+      <c r="B195" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C195" s="0" t="n">
+      <c r="C195" s="11" t="n">
         <v>16.88</v>
       </c>
-      <c r="D195" s="0" t="n">
+      <c r="D195" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="0" t="n">
+      <c r="A196" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B196" s="0" t="s">
+      <c r="B196" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C196" s="0" t="n">
+      <c r="C196" s="11" t="n">
         <v>13.73</v>
       </c>
-      <c r="D196" s="0" t="n">
+      <c r="D196" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B197" s="0" t="s">
+      <c r="A197" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B197" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C197" s="0" t="n">
+      <c r="C197" s="11" t="n">
         <v>16.28</v>
       </c>
-      <c r="D197" s="0" t="n">
+      <c r="D197" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B198" s="0" t="s">
+      <c r="A198" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B198" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C198" s="0" t="n">
+      <c r="C198" s="11" t="n">
         <v>16.22</v>
       </c>
-      <c r="D198" s="0" t="n">
+      <c r="D198" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="0" t="n">
+      <c r="A199" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B199" s="0" t="s">
+      <c r="B199" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C199" s="0" t="n">
+      <c r="C199" s="11" t="n">
         <v>13.83</v>
       </c>
-      <c r="D199" s="0" t="n">
+      <c r="D199" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="0" t="n">
+      <c r="A200" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B200" s="0" t="s">
+      <c r="B200" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C200" s="0" t="n">
+      <c r="C200" s="11" t="n">
         <v>15.84</v>
       </c>
-      <c r="D200" s="0" t="n">
+      <c r="D200" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="0" t="n">
+      <c r="A201" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B201" s="0" t="s">
+      <c r="B201" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C201" s="0" t="n">
+      <c r="C201" s="11" t="n">
         <v>13.75</v>
       </c>
-      <c r="D201" s="0" t="n">
+      <c r="D201" s="11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="0" t="n">
+      <c r="A202" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B202" s="0" t="s">
+      <c r="B202" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C202" s="0" t="n">
+      <c r="C202" s="11" t="n">
         <v>25.59</v>
       </c>
-      <c r="D202" s="0" t="n">
+      <c r="D202" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="0" t="n">
+      <c r="A203" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B203" s="0" t="s">
+      <c r="B203" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C203" s="0" t="n">
+      <c r="C203" s="11" t="n">
         <v>19.58</v>
       </c>
-      <c r="D203" s="0" t="n">
+      <c r="D203" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="0" t="n">
+      <c r="A204" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B204" s="0" t="s">
+      <c r="B204" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C204" s="0" t="n">
+      <c r="C204" s="11" t="n">
         <v>24.62</v>
       </c>
-      <c r="D204" s="0" t="n">
+      <c r="D204" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="0" t="n">
+      <c r="A205" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B205" s="0" t="s">
+      <c r="B205" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C205" s="0" t="n">
+      <c r="C205" s="11" t="n">
         <v>24.61</v>
       </c>
-      <c r="D205" s="0" t="n">
+      <c r="D205" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="0" t="n">
+      <c r="A206" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B206" s="0" t="s">
+      <c r="B206" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C206" s="0" t="n">
+      <c r="C206" s="11" t="n">
         <v>24.78</v>
       </c>
-      <c r="D206" s="0" t="n">
+      <c r="D206" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="0" t="n">
+      <c r="A207" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B207" s="0" t="s">
+      <c r="B207" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C207" s="0" t="n">
+      <c r="C207" s="11" t="n">
         <v>26.05</v>
       </c>
-      <c r="D207" s="0" t="n">
+      <c r="D207" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="0" t="n">
+      <c r="A208" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B208" s="0" t="s">
+      <c r="B208" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C208" s="0" t="n">
+      <c r="C208" s="11" t="n">
         <v>23.06</v>
       </c>
-      <c r="D208" s="0" t="n">
+      <c r="D208" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="0" t="n">
+      <c r="A209" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B209" s="0" t="s">
+      <c r="B209" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C209" s="0" t="n">
+      <c r="C209" s="11" t="n">
         <v>22.98</v>
       </c>
-      <c r="D209" s="0" t="n">
+      <c r="D209" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B210" s="0" t="s">
+      <c r="A210" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B210" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C210" s="0" t="n">
+      <c r="C210" s="11" t="n">
         <v>23.02</v>
       </c>
-      <c r="D210" s="0" t="n">
+      <c r="D210" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="0" t="n">
+      <c r="A211" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B211" s="0" t="s">
+      <c r="B211" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="C211" s="0" t="n">
+      <c r="C211" s="11" t="n">
         <v>23.86</v>
       </c>
-      <c r="D211" s="0" t="n">
+      <c r="D211" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="0" t="n">
+      <c r="A212" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B212" s="0" t="s">
+      <c r="B212" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C212" s="0" t="n">
+      <c r="C212" s="11" t="n">
         <v>18.86</v>
       </c>
-      <c r="D212" s="0" t="n">
+      <c r="D212" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="0" t="n">
+      <c r="A213" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B213" s="0" t="s">
+      <c r="B213" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C213" s="0" t="n">
+      <c r="C213" s="11" t="n">
         <v>16.15</v>
       </c>
-      <c r="D213" s="0" t="n">
+      <c r="D213" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="0" t="n">
+      <c r="A214" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B214" s="0" t="s">
+      <c r="B214" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C214" s="0" t="n">
+      <c r="C214" s="11" t="n">
         <v>13.85</v>
       </c>
-      <c r="D214" s="0" t="n">
+      <c r="D214" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="0" t="n">
+      <c r="A215" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B215" s="0" t="s">
+      <c r="B215" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C215" s="0" t="n">
+      <c r="C215" s="11" t="n">
         <v>16.55</v>
       </c>
-      <c r="D215" s="0" t="n">
+      <c r="D215" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="0" t="n">
+      <c r="A216" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B216" s="0" t="s">
+      <c r="B216" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C216" s="0" t="n">
+      <c r="C216" s="11" t="n">
         <v>14.03</v>
       </c>
-      <c r="D216" s="0" t="n">
+      <c r="D216" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B217" s="0" t="s">
+      <c r="A217" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B217" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C217" s="0" t="n">
+      <c r="C217" s="11" t="n">
         <v>15.12</v>
       </c>
-      <c r="D217" s="0" t="n">
+      <c r="D217" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B218" s="0" t="s">
+      <c r="A218" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B218" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C218" s="0" t="n">
+      <c r="C218" s="11" t="n">
         <v>15.12</v>
       </c>
-      <c r="D218" s="0" t="n">
+      <c r="D218" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="0" t="n">
+      <c r="A219" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B219" s="0" t="s">
+      <c r="B219" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C219" s="0" t="n">
+      <c r="C219" s="11" t="n">
         <v>13.38</v>
       </c>
-      <c r="D219" s="0" t="n">
+      <c r="D219" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="0" t="n">
+      <c r="A220" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B220" s="0" t="s">
+      <c r="B220" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C220" s="0" t="n">
+      <c r="C220" s="11" t="n">
         <v>15.26</v>
       </c>
-      <c r="D220" s="0" t="n">
+      <c r="D220" s="11" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="0" t="n">
+      <c r="A221" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B221" s="0" t="s">
+      <c r="B221" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C221" s="0" t="n">
+      <c r="C221" s="11" t="n">
         <v>12.91</v>
       </c>
-      <c r="D221" s="0" t="n">
+      <c r="D221" s="11" t="n">
         <v>11</v>
       </c>
     </row>
